--- a/research/traditional_assets/database/data/palestinian_authority/palestinian_authority_real_estate_development.xlsx
+++ b/research/traditional_assets/database/data/palestinian_authority/palestinian_authority_real_estate_development.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="plse_prico" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,121 +590,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.004000000000000004</v>
+        <v>-0.07839500000000001</v>
       </c>
       <c r="E2">
-        <v>0.287</v>
+        <v>-0.318</v>
       </c>
       <c r="G2">
-        <v>0.1015655577299413</v>
+        <v>0.4414490311710194</v>
       </c>
       <c r="H2">
-        <v>0.1015655577299413</v>
+        <v>0.4414490311710194</v>
       </c>
       <c r="I2">
-        <v>0.1134050880626223</v>
+        <v>0.339932603201348</v>
       </c>
       <c r="J2">
-        <v>0.109383453882428</v>
+        <v>0.1980810281812366</v>
       </c>
       <c r="K2">
-        <v>-1.61</v>
+        <v>-0.115</v>
       </c>
       <c r="L2">
-        <v>-0.1575342465753425</v>
+        <v>-0.009688289806234204</v>
       </c>
       <c r="M2">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.0149812734082397</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.4968944099378881</v>
+        <v>-0</v>
       </c>
       <c r="P2">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.0149812734082397</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>-0.4968944099378881</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>6.489999999999999</v>
+        <v>8.59</v>
       </c>
       <c r="V2">
-        <v>0.1215355805243445</v>
+        <v>0.1756646216768916</v>
       </c>
       <c r="W2">
-        <v>-0.009407644094875267</v>
+        <v>-0.000895856720073477</v>
       </c>
       <c r="X2">
-        <v>0.05439786287507575</v>
+        <v>0.1039676224700963</v>
       </c>
       <c r="Y2">
-        <v>-0.06380550696995102</v>
+        <v>-0.1048634791901698</v>
       </c>
       <c r="Z2">
-        <v>0.08573825503355706</v>
+        <v>0.1050163673361055</v>
       </c>
       <c r="AA2">
-        <v>0.0134755483416447</v>
+        <v>0.01481729619801431</v>
       </c>
       <c r="AB2">
-        <v>0.04538586413426307</v>
+        <v>0.08713975562860812</v>
       </c>
       <c r="AC2">
-        <v>-0.03191031579261837</v>
+        <v>-0.07232245943059382</v>
       </c>
       <c r="AD2">
-        <v>30.72</v>
+        <v>30.46</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>30.72</v>
+        <v>30.46</v>
       </c>
       <c r="AG2">
-        <v>24.23</v>
+        <v>21.87</v>
       </c>
       <c r="AH2">
-        <v>0.3651925820256776</v>
+        <v>0.383820564516129</v>
       </c>
       <c r="AI2">
-        <v>0.2443525294304804</v>
+        <v>0.2425931825422109</v>
       </c>
       <c r="AJ2">
-        <v>0.3121216024732706</v>
+        <v>0.3090292496820686</v>
       </c>
       <c r="AK2">
-        <v>0.2032206659397802</v>
+        <v>0.1869710182097974</v>
       </c>
       <c r="AL2">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="AM2">
-        <v>1.383</v>
+        <v>1.091</v>
       </c>
       <c r="AN2">
-        <v>8.020887728459529</v>
+        <v>4.88375821709155</v>
       </c>
       <c r="AO2">
-        <v>0.7067073170731708</v>
+        <v>2.782758620689656</v>
       </c>
       <c r="AP2">
-        <v>6.326370757180157</v>
+        <v>3.506493506493507</v>
       </c>
       <c r="AQ2">
-        <v>0.8380332610267535</v>
+        <v>3.698441796516957</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +712,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Union Construction and Investment (PLSE:UCI)</t>
+          <t>Palestine Real Estate Investment CO. PLC (PLSE:PRICO)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,118 +721,115 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.132</v>
-      </c>
-      <c r="E3">
-        <v>0.287</v>
+        <v>0.00821</v>
       </c>
       <c r="G3">
-        <v>0.08695652173913045</v>
+        <v>0.3716981132075472</v>
       </c>
       <c r="H3">
-        <v>0.08695652173913045</v>
+        <v>0.3716981132075472</v>
       </c>
       <c r="I3">
-        <v>0.466403162055336</v>
+        <v>0.3650943396226415</v>
       </c>
       <c r="J3">
-        <v>0.4333234664205743</v>
+        <v>0.1825471698113208</v>
       </c>
       <c r="K3">
-        <v>2.11</v>
+        <v>-0.292</v>
       </c>
       <c r="L3">
-        <v>0.8339920948616601</v>
+        <v>-0.02754716981132075</v>
       </c>
       <c r="M3">
-        <v>0.8</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.04166666666666667</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.3791469194312796</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>0.8</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.04166666666666667</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.3791469194312796</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>5.02</v>
+        <v>2.21</v>
       </c>
       <c r="V3">
-        <v>0.2614583333333333</v>
+        <v>0.06461988304093566</v>
       </c>
       <c r="W3">
-        <v>0.05341772151898734</v>
+        <v>-0.006108786610878661</v>
       </c>
       <c r="X3">
-        <v>0.04966336942837775</v>
+        <v>0.1041378617944074</v>
       </c>
       <c r="Y3">
-        <v>0.003754352090609592</v>
+        <v>-0.1102466484052861</v>
       </c>
       <c r="Z3">
-        <v>0.06281032770605759</v>
+        <v>0.1477763836609508</v>
       </c>
       <c r="AA3">
-        <v>0.02721718892860111</v>
+        <v>0.02697616060225847</v>
       </c>
       <c r="AB3">
-        <v>0.04571895344710818</v>
+        <v>0.08529779538409149</v>
       </c>
       <c r="AC3">
-        <v>-0.01850176451850706</v>
+        <v>-0.05832163478183301</v>
       </c>
       <c r="AD3">
-        <v>5.32</v>
+        <v>21.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>5.32</v>
+        <v>21.4</v>
       </c>
       <c r="AG3">
-        <v>0.3000000000000007</v>
+        <v>19.19</v>
       </c>
       <c r="AH3">
-        <v>0.2169657422512235</v>
+        <v>0.3848920863309352</v>
       </c>
       <c r="AI3">
-        <v>0.114853195164076</v>
+        <v>0.2838196286472148</v>
       </c>
       <c r="AJ3">
-        <v>0.01538461538461542</v>
+        <v>0.3594306049822064</v>
       </c>
       <c r="AK3">
-        <v>0.007263922518159824</v>
+        <v>0.2621942888372728</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AM3">
-        <v>-0.127</v>
+        <v>1.195</v>
       </c>
       <c r="AN3">
-        <v>4.32520325203252</v>
+        <v>3.543046357615894</v>
+      </c>
+      <c r="AO3">
+        <v>2.66896551724138</v>
       </c>
       <c r="AP3">
-        <v>0.2439024390243908</v>
+        <v>3.177152317880794</v>
       </c>
       <c r="AQ3">
-        <v>-9.291338582677165</v>
+        <v>3.238493723849373</v>
       </c>
     </row>
     <row r="4">
@@ -844,7 +840,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Palestine Real Estate Investment CO. PLC (PLSE:PRICO)</t>
+          <t>Union Construction and Investment (PLSE:UCI)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -853,25 +849,28 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.124</v>
+        <v>-0.165</v>
+      </c>
+      <c r="E4">
+        <v>-0.318</v>
       </c>
       <c r="G4">
-        <v>0.106371911573472</v>
+        <v>1.023622047244094</v>
       </c>
       <c r="H4">
-        <v>0.106371911573472</v>
+        <v>1.023622047244094</v>
       </c>
       <c r="I4">
-        <v>-0.002730819245773732</v>
+        <v>0.1299212598425197</v>
       </c>
       <c r="J4">
-        <v>-0.002730819245773732</v>
+        <v>0.08645136463205258</v>
       </c>
       <c r="K4">
-        <v>-3.72</v>
+        <v>0.177</v>
       </c>
       <c r="L4">
-        <v>-0.4837451235370611</v>
+        <v>0.1393700787401575</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -880,7 +879,7 @@
         <v>-0</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -889,79 +888,8788 @@
         <v>-0</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1.47</v>
+        <v>6.38</v>
       </c>
       <c r="V4">
-        <v>0.04298245614035087</v>
+        <v>0.4340136054421769</v>
       </c>
       <c r="W4">
-        <v>-0.07223300970873787</v>
+        <v>0.004317073170731707</v>
       </c>
       <c r="X4">
-        <v>0.05913235632177376</v>
+        <v>0.1037973831457851</v>
       </c>
       <c r="Y4">
-        <v>-0.1313653660305116</v>
+        <v>-0.09948030997505342</v>
       </c>
       <c r="Z4">
-        <v>0.0974404460212874</v>
+        <v>0.03075060532687652</v>
       </c>
       <c r="AA4">
-        <v>-0.0002660922453117081</v>
+        <v>0.00265843179377014</v>
       </c>
       <c r="AB4">
-        <v>0.04505277482141797</v>
+        <v>0.08898171587312477</v>
       </c>
       <c r="AC4">
-        <v>-0.04531886706672968</v>
+        <v>-0.08632328407935463</v>
       </c>
       <c r="AD4">
-        <v>25.4</v>
+        <v>9.06</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>25.4</v>
+        <v>9.06</v>
       </c>
       <c r="AG4">
-        <v>23.93</v>
+        <v>2.680000000000001</v>
       </c>
       <c r="AH4">
-        <v>0.4261744966442952</v>
+        <v>0.3813131313131314</v>
       </c>
       <c r="AI4">
-        <v>0.3198992443324937</v>
+        <v>0.180622009569378</v>
       </c>
       <c r="AJ4">
-        <v>0.4116635128161018</v>
+        <v>0.1542002301495973</v>
       </c>
       <c r="AK4">
-        <v>0.3070704478378031</v>
+        <v>0.06121516674280494</v>
       </c>
       <c r="AL4">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>1.51</v>
+        <v>-0.104</v>
       </c>
       <c r="AN4">
-        <v>9.769230769230768</v>
-      </c>
-      <c r="AO4">
-        <v>-0.01280487804878049</v>
+        <v>45.98984771573604</v>
       </c>
       <c r="AP4">
-        <v>9.203846153846154</v>
+        <v>13.60406091370559</v>
       </c>
       <c r="AQ4">
-        <v>-0.01390728476821192</v>
+        <v>-1.586538461538462</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Palestine Real Estate Investment CO. PLC (PLSE:PRICO)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PLSE:PRICO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Real Estate (Development)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Palestinian Authority</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.384892086330935</v>
+      </c>
+      <c r="F2">
+        <v>0.17</v>
+      </c>
+      <c r="G2">
+        <v>34.2</v>
+      </c>
+      <c r="H2">
+        <v>49.434741759191</v>
+      </c>
+      <c r="I2">
+        <v>53.39</v>
+      </c>
+      <c r="J2">
+        <v>56.676741759191</v>
+      </c>
+      <c r="K2">
+        <v>21.4</v>
+      </c>
+      <c r="L2">
+        <v>9.452</v>
+      </c>
+      <c r="M2">
+        <v>0.0852977953840915</v>
+      </c>
+      <c r="N2">
+        <v>0.08037589673570431</v>
+      </c>
+      <c r="O2">
+        <v>0.0551889042049885</v>
+      </c>
+      <c r="P2">
+        <v>0.0387621289144639</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.104137861794407</v>
+      </c>
+      <c r="T2">
+        <v>0.08889919857860901</v>
+      </c>
+      <c r="U2">
+        <v>0.77593914788517</v>
+      </c>
+      <c r="V2">
+        <v>0.59496788519246</v>
+      </c>
+      <c r="W2">
+        <v>13.50367768598868</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>34.2</v>
+      </c>
+      <c r="AB2">
+        <v>0.08420487865895976</v>
+      </c>
+      <c r="AC2">
+        <v>0.06506693499042704</v>
+      </c>
+      <c r="AD2">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>6.04</v>
+      </c>
+      <c r="AH2">
+        <v>0.207</v>
+      </c>
+      <c r="AI2">
+        <v>0.625</v>
+      </c>
+      <c r="AJ2">
+        <v>21.4</v>
+      </c>
+      <c r="AK2">
+        <v>21.4</v>
+      </c>
+      <c r="AL2">
+        <v>1.45</v>
+      </c>
+      <c r="AM2">
+        <v>21.4</v>
+      </c>
+      <c r="AN2">
+        <v>2.21</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.08148393343493208</v>
+      </c>
+      <c r="C2">
+        <v>58.11200436236422</v>
+      </c>
+      <c r="D2">
+        <v>55.90200436236422</v>
+      </c>
+      <c r="E2">
+        <v>-21.4</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>2.21</v>
+      </c>
+      <c r="H2">
+        <v>34.2</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>6.04</v>
+      </c>
+      <c r="K2">
+        <v>0.207</v>
+      </c>
+      <c r="L2">
+        <v>5.833</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>5.833</v>
+      </c>
+      <c r="O2">
+        <v>0.8855273969788223</v>
+      </c>
+      <c r="P2">
+        <v>4.947472603021178</v>
+      </c>
+      <c r="Q2">
+        <v>5.154472603021178</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.08148393343493208</v>
+      </c>
+      <c r="T2">
+        <v>0.5069057056397804</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W2">
+        <v>0.03876212891446389</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.08141875480556576</v>
+      </c>
+      <c r="C3">
+        <v>57.60099036993891</v>
+      </c>
+      <c r="D3">
+        <v>55.94699036993891</v>
+      </c>
+      <c r="E3">
+        <v>-20.844</v>
+      </c>
+      <c r="F3">
+        <v>0.556</v>
+      </c>
+      <c r="G3">
+        <v>2.21</v>
+      </c>
+      <c r="H3">
+        <v>34.2</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>6.04</v>
+      </c>
+      <c r="K3">
+        <v>0.207</v>
+      </c>
+      <c r="L3">
+        <v>5.833</v>
+      </c>
+      <c r="M3">
+        <v>0.0254092</v>
+      </c>
+      <c r="N3">
+        <v>5.8075908</v>
+      </c>
+      <c r="O3">
+        <v>0.8816699406552642</v>
+      </c>
+      <c r="P3">
+        <v>4.925920859344735</v>
+      </c>
+      <c r="Q3">
+        <v>5.132920859344735</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.08184962981456678</v>
+      </c>
+      <c r="T3">
+        <v>0.5112486414109465</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W3">
+        <v>0.03876212891446389</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>229.5625206618075</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.0813535761761994</v>
+      </c>
+      <c r="C4">
+        <v>57.09004883898533</v>
+      </c>
+      <c r="D4">
+        <v>55.99204883898533</v>
+      </c>
+      <c r="E4">
+        <v>-20.288</v>
+      </c>
+      <c r="F4">
+        <v>1.112</v>
+      </c>
+      <c r="G4">
+        <v>2.21</v>
+      </c>
+      <c r="H4">
+        <v>34.2</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>6.04</v>
+      </c>
+      <c r="K4">
+        <v>0.207</v>
+      </c>
+      <c r="L4">
+        <v>5.833</v>
+      </c>
+      <c r="M4">
+        <v>0.05081840000000001</v>
+      </c>
+      <c r="N4">
+        <v>5.7821816</v>
+      </c>
+      <c r="O4">
+        <v>0.8778124843317062</v>
+      </c>
+      <c r="P4">
+        <v>4.904369115668294</v>
+      </c>
+      <c r="Q4">
+        <v>5.111369115668294</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.08222278938562258</v>
+      </c>
+      <c r="T4">
+        <v>0.5156802085243811</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W4">
+        <v>0.03876212891446389</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>114.7812603309038</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.08128839754683308</v>
+      </c>
+      <c r="C5">
+        <v>56.57917994472115</v>
+      </c>
+      <c r="D5">
+        <v>56.03717994472115</v>
+      </c>
+      <c r="E5">
+        <v>-19.732</v>
+      </c>
+      <c r="F5">
+        <v>1.668</v>
+      </c>
+      <c r="G5">
+        <v>2.21</v>
+      </c>
+      <c r="H5">
+        <v>34.2</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>6.04</v>
+      </c>
+      <c r="K5">
+        <v>0.207</v>
+      </c>
+      <c r="L5">
+        <v>5.833</v>
+      </c>
+      <c r="M5">
+        <v>0.07622760000000001</v>
+      </c>
+      <c r="N5">
+        <v>5.7567724</v>
+      </c>
+      <c r="O5">
+        <v>0.8739550280081481</v>
+      </c>
+      <c r="P5">
+        <v>4.882817371991852</v>
+      </c>
+      <c r="Q5">
+        <v>5.089817371991852</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.08260364296845274</v>
+      </c>
+      <c r="T5">
+        <v>0.5202031481556186</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W5">
+        <v>0.03876212891446389</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>76.52084022060251</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.08122321891746673</v>
+      </c>
+      <c r="C6">
+        <v>56.06838386292949</v>
+      </c>
+      <c r="D6">
+        <v>56.08238386292949</v>
+      </c>
+      <c r="E6">
+        <v>-19.176</v>
+      </c>
+      <c r="F6">
+        <v>2.224</v>
+      </c>
+      <c r="G6">
+        <v>2.21</v>
+      </c>
+      <c r="H6">
+        <v>34.2</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>6.04</v>
+      </c>
+      <c r="K6">
+        <v>0.207</v>
+      </c>
+      <c r="L6">
+        <v>5.833</v>
+      </c>
+      <c r="M6">
+        <v>0.1016368</v>
+      </c>
+      <c r="N6">
+        <v>5.731363200000001</v>
+      </c>
+      <c r="O6">
+        <v>0.87009757168459</v>
+      </c>
+      <c r="P6">
+        <v>4.861265628315411</v>
+      </c>
+      <c r="Q6">
+        <v>5.068265628315411</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.08299243100092518</v>
+      </c>
+      <c r="T6">
+        <v>0.5248203156958403</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W6">
+        <v>0.03876212891446389</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>57.39063016545188</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.08115804028810039</v>
+      </c>
+      <c r="C7">
+        <v>55.5576607699611</v>
+      </c>
+      <c r="D7">
+        <v>56.1276607699611</v>
+      </c>
+      <c r="E7">
+        <v>-18.62</v>
+      </c>
+      <c r="F7">
+        <v>2.78</v>
+      </c>
+      <c r="G7">
+        <v>2.21</v>
+      </c>
+      <c r="H7">
+        <v>34.2</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>6.04</v>
+      </c>
+      <c r="K7">
+        <v>0.207</v>
+      </c>
+      <c r="L7">
+        <v>5.833</v>
+      </c>
+      <c r="M7">
+        <v>0.127046</v>
+      </c>
+      <c r="N7">
+        <v>5.705954</v>
+      </c>
+      <c r="O7">
+        <v>0.866240115361032</v>
+      </c>
+      <c r="P7">
+        <v>4.839713884638968</v>
+      </c>
+      <c r="Q7">
+        <v>5.046713884638968</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.08338940404460758</v>
+      </c>
+      <c r="T7">
+        <v>0.5295346867632245</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W7">
+        <v>0.03876212891446389</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>45.9125041323615</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.08109286165873404</v>
+      </c>
+      <c r="C8">
+        <v>55.04701084273669</v>
+      </c>
+      <c r="D8">
+        <v>56.17301084273669</v>
+      </c>
+      <c r="E8">
+        <v>-18.064</v>
+      </c>
+      <c r="F8">
+        <v>3.336</v>
+      </c>
+      <c r="G8">
+        <v>2.21</v>
+      </c>
+      <c r="H8">
+        <v>34.2</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>6.04</v>
+      </c>
+      <c r="K8">
+        <v>0.207</v>
+      </c>
+      <c r="L8">
+        <v>5.833</v>
+      </c>
+      <c r="M8">
+        <v>0.1524552</v>
+      </c>
+      <c r="N8">
+        <v>5.6805448</v>
+      </c>
+      <c r="O8">
+        <v>0.8623826590374738</v>
+      </c>
+      <c r="P8">
+        <v>4.818162140962526</v>
+      </c>
+      <c r="Q8">
+        <v>5.025162140962526</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.08379482332326194</v>
+      </c>
+      <c r="T8">
+        <v>0.5343493635979998</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W8">
+        <v>0.03876212891446389</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>38.26042011030125</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.08102768302936772</v>
+      </c>
+      <c r="C9">
+        <v>54.53643425874921</v>
+      </c>
+      <c r="D9">
+        <v>56.21843425874921</v>
+      </c>
+      <c r="E9">
+        <v>-17.508</v>
+      </c>
+      <c r="F9">
+        <v>3.892</v>
+      </c>
+      <c r="G9">
+        <v>2.21</v>
+      </c>
+      <c r="H9">
+        <v>34.2</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>6.04</v>
+      </c>
+      <c r="K9">
+        <v>0.207</v>
+      </c>
+      <c r="L9">
+        <v>5.833</v>
+      </c>
+      <c r="M9">
+        <v>0.1778644</v>
+      </c>
+      <c r="N9">
+        <v>5.6551356</v>
+      </c>
+      <c r="O9">
+        <v>0.8585252027139157</v>
+      </c>
+      <c r="P9">
+        <v>4.796610397286084</v>
+      </c>
+      <c r="Q9">
+        <v>5.003610397286084</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.08420896129608091</v>
+      </c>
+      <c r="T9">
+        <v>0.5392675818700821</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W9">
+        <v>0.03876212891446389</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>32.79464580882964</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.08096250440000138</v>
+      </c>
+      <c r="C10">
+        <v>54.0259311960662</v>
+      </c>
+      <c r="D10">
+        <v>56.2639311960662</v>
+      </c>
+      <c r="E10">
+        <v>-16.952</v>
+      </c>
+      <c r="F10">
+        <v>4.448</v>
+      </c>
+      <c r="G10">
+        <v>2.21</v>
+      </c>
+      <c r="H10">
+        <v>34.2</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>6.04</v>
+      </c>
+      <c r="K10">
+        <v>0.207</v>
+      </c>
+      <c r="L10">
+        <v>5.833</v>
+      </c>
+      <c r="M10">
+        <v>0.2032736</v>
+      </c>
+      <c r="N10">
+        <v>5.6297264</v>
+      </c>
+      <c r="O10">
+        <v>0.8546677463903577</v>
+      </c>
+      <c r="P10">
+        <v>4.775058653609642</v>
+      </c>
+      <c r="Q10">
+        <v>4.982058653609642</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.084632102268309</v>
+      </c>
+      <c r="T10">
+        <v>0.544292717930688</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W10">
+        <v>0.03876212891446389</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>28.69531508272594</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.08089732577063503</v>
+      </c>
+      <c r="C11">
+        <v>53.51550183333212</v>
+      </c>
+      <c r="D11">
+        <v>56.30950183333211</v>
+      </c>
+      <c r="E11">
+        <v>-16.396</v>
+      </c>
+      <c r="F11">
+        <v>5.004</v>
+      </c>
+      <c r="G11">
+        <v>2.21</v>
+      </c>
+      <c r="H11">
+        <v>34.2</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>6.04</v>
+      </c>
+      <c r="K11">
+        <v>0.207</v>
+      </c>
+      <c r="L11">
+        <v>5.833</v>
+      </c>
+      <c r="M11">
+        <v>0.2286828</v>
+      </c>
+      <c r="N11">
+        <v>5.604317200000001</v>
+      </c>
+      <c r="O11">
+        <v>0.8508102900667996</v>
+      </c>
+      <c r="P11">
+        <v>4.753506909933201</v>
+      </c>
+      <c r="Q11">
+        <v>4.9605069099332</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.08506454304212449</v>
+      </c>
+      <c r="T11">
+        <v>0.5494282965420764</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W11">
+        <v>0.03876212891446389</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>25.50694674020084</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.08083214714126871</v>
+      </c>
+      <c r="C12">
+        <v>53.00514634977058</v>
+      </c>
+      <c r="D12">
+        <v>56.35514634977058</v>
+      </c>
+      <c r="E12">
+        <v>-15.84</v>
+      </c>
+      <c r="F12">
+        <v>5.56</v>
+      </c>
+      <c r="G12">
+        <v>2.21</v>
+      </c>
+      <c r="H12">
+        <v>34.2</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>6.04</v>
+      </c>
+      <c r="K12">
+        <v>0.207</v>
+      </c>
+      <c r="L12">
+        <v>5.833</v>
+      </c>
+      <c r="M12">
+        <v>0.254092</v>
+      </c>
+      <c r="N12">
+        <v>5.578908</v>
+      </c>
+      <c r="O12">
+        <v>0.8469528337432415</v>
+      </c>
+      <c r="P12">
+        <v>4.731955166256759</v>
+      </c>
+      <c r="Q12">
+        <v>4.938955166256759</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.08550659361091369</v>
+      </c>
+      <c r="T12">
+        <v>0.5546779991226067</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W12">
+        <v>0.03876212891446389</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>22.95625206618075</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.08076696851190238</v>
+      </c>
+      <c r="C13">
+        <v>52.4948649251869</v>
+      </c>
+      <c r="D13">
+        <v>56.40086492518689</v>
+      </c>
+      <c r="E13">
+        <v>-15.284</v>
+      </c>
+      <c r="F13">
+        <v>6.116000000000001</v>
+      </c>
+      <c r="G13">
+        <v>2.21</v>
+      </c>
+      <c r="H13">
+        <v>34.2</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>6.04</v>
+      </c>
+      <c r="K13">
+        <v>0.207</v>
+      </c>
+      <c r="L13">
+        <v>5.833</v>
+      </c>
+      <c r="M13">
+        <v>0.2795012000000001</v>
+      </c>
+      <c r="N13">
+        <v>5.5534988</v>
+      </c>
+      <c r="O13">
+        <v>0.8430953774196834</v>
+      </c>
+      <c r="P13">
+        <v>4.710403422580317</v>
+      </c>
+      <c r="Q13">
+        <v>4.917403422580317</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.08595857790034983</v>
+      </c>
+      <c r="T13">
+        <v>0.5600456725476434</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W13">
+        <v>0.03876212891446389</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>20.86932006016432</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.08070178988253603</v>
+      </c>
+      <c r="C14">
+        <v>51.98465773997025</v>
+      </c>
+      <c r="D14">
+        <v>56.44665773997025</v>
+      </c>
+      <c r="E14">
+        <v>-14.728</v>
+      </c>
+      <c r="F14">
+        <v>6.672</v>
+      </c>
+      <c r="G14">
+        <v>2.21</v>
+      </c>
+      <c r="H14">
+        <v>34.2</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>6.04</v>
+      </c>
+      <c r="K14">
+        <v>0.207</v>
+      </c>
+      <c r="L14">
+        <v>5.833</v>
+      </c>
+      <c r="M14">
+        <v>0.3049104</v>
+      </c>
+      <c r="N14">
+        <v>5.5280896</v>
+      </c>
+      <c r="O14">
+        <v>0.8392379210961254</v>
+      </c>
+      <c r="P14">
+        <v>4.688851678903875</v>
+      </c>
+      <c r="Q14">
+        <v>4.895851678903875</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.08642083456000041</v>
+      </c>
+      <c r="T14">
+        <v>0.5655353385505217</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W14">
+        <v>0.03876212891446389</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>19.13021005515063</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.0806366112531697</v>
+      </c>
+      <c r="C15">
+        <v>51.47452497509615</v>
+      </c>
+      <c r="D15">
+        <v>56.49252497509615</v>
+      </c>
+      <c r="E15">
+        <v>-14.172</v>
+      </c>
+      <c r="F15">
+        <v>7.228000000000001</v>
+      </c>
+      <c r="G15">
+        <v>2.21</v>
+      </c>
+      <c r="H15">
+        <v>34.2</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>6.04</v>
+      </c>
+      <c r="K15">
+        <v>0.207</v>
+      </c>
+      <c r="L15">
+        <v>5.833</v>
+      </c>
+      <c r="M15">
+        <v>0.3303196</v>
+      </c>
+      <c r="N15">
+        <v>5.5026804</v>
+      </c>
+      <c r="O15">
+        <v>0.8353804647725672</v>
+      </c>
+      <c r="P15">
+        <v>4.667299935227433</v>
+      </c>
+      <c r="Q15">
+        <v>4.874299935227433</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.08689371780952804</v>
+      </c>
+      <c r="T15">
+        <v>0.5711512037718572</v>
+      </c>
+      <c r="U15">
+        <v>0.0457</v>
+      </c>
+      <c r="V15">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W15">
+        <v>0.03876212891446389</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>17.65865543552366</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.08057143262380335</v>
+      </c>
+      <c r="C16">
+        <v>50.96446681212885</v>
+      </c>
+      <c r="D16">
+        <v>56.53846681212885</v>
+      </c>
+      <c r="E16">
+        <v>-13.616</v>
+      </c>
+      <c r="F16">
+        <v>7.784000000000001</v>
+      </c>
+      <c r="G16">
+        <v>2.21</v>
+      </c>
+      <c r="H16">
+        <v>34.2</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>6.04</v>
+      </c>
+      <c r="K16">
+        <v>0.207</v>
+      </c>
+      <c r="L16">
+        <v>5.833</v>
+      </c>
+      <c r="M16">
+        <v>0.3557288000000001</v>
+      </c>
+      <c r="N16">
+        <v>5.477271200000001</v>
+      </c>
+      <c r="O16">
+        <v>0.8315230084490093</v>
+      </c>
+      <c r="P16">
+        <v>4.645748191550991</v>
+      </c>
+      <c r="Q16">
+        <v>4.852748191550991</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.08737759834392839</v>
+      </c>
+      <c r="T16">
+        <v>0.5768976705099679</v>
+      </c>
+      <c r="U16">
+        <v>0.0457</v>
+      </c>
+      <c r="V16">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W16">
+        <v>0.03876212891446389</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>16.39732290441482</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.08050625399443702</v>
+      </c>
+      <c r="C17">
+        <v>50.45448343322367</v>
+      </c>
+      <c r="D17">
+        <v>56.58448343322367</v>
+      </c>
+      <c r="E17">
+        <v>-13.06</v>
+      </c>
+      <c r="F17">
+        <v>8.34</v>
+      </c>
+      <c r="G17">
+        <v>2.21</v>
+      </c>
+      <c r="H17">
+        <v>34.2</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>6.04</v>
+      </c>
+      <c r="K17">
+        <v>0.207</v>
+      </c>
+      <c r="L17">
+        <v>5.833</v>
+      </c>
+      <c r="M17">
+        <v>0.381138</v>
+      </c>
+      <c r="N17">
+        <v>5.451862</v>
+      </c>
+      <c r="O17">
+        <v>0.8276655521254511</v>
+      </c>
+      <c r="P17">
+        <v>4.624196447874549</v>
+      </c>
+      <c r="Q17">
+        <v>4.831196447874549</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.08787286430266758</v>
+      </c>
+      <c r="T17">
+        <v>0.5827793482301517</v>
+      </c>
+      <c r="U17">
+        <v>0.0457</v>
+      </c>
+      <c r="V17">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W17">
+        <v>0.03876212891446389</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>15.3041680441205</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.08044107536507067</v>
+      </c>
+      <c r="C18">
+        <v>49.94457502112947</v>
+      </c>
+      <c r="D18">
+        <v>56.63057502112947</v>
+      </c>
+      <c r="E18">
+        <v>-12.504</v>
+      </c>
+      <c r="F18">
+        <v>8.896000000000001</v>
+      </c>
+      <c r="G18">
+        <v>2.21</v>
+      </c>
+      <c r="H18">
+        <v>34.2</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>6.04</v>
+      </c>
+      <c r="K18">
+        <v>0.207</v>
+      </c>
+      <c r="L18">
+        <v>5.833</v>
+      </c>
+      <c r="M18">
+        <v>0.4065472000000001</v>
+      </c>
+      <c r="N18">
+        <v>5.4264528</v>
+      </c>
+      <c r="O18">
+        <v>0.823808095801893</v>
+      </c>
+      <c r="P18">
+        <v>4.602644704198107</v>
+      </c>
+      <c r="Q18">
+        <v>4.809644704198107</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.0883799223080434</v>
+      </c>
+      <c r="T18">
+        <v>0.5888010658960541</v>
+      </c>
+      <c r="U18">
+        <v>0.0457</v>
+      </c>
+      <c r="V18">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W18">
+        <v>0.03876212891446389</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>14.34765754136297</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.08037589673570433</v>
+      </c>
+      <c r="C19">
+        <v>49.43474175919096</v>
+      </c>
+      <c r="D19">
+        <v>56.67674175919096</v>
+      </c>
+      <c r="E19">
+        <v>-11.948</v>
+      </c>
+      <c r="F19">
+        <v>9.452000000000002</v>
+      </c>
+      <c r="G19">
+        <v>2.21</v>
+      </c>
+      <c r="H19">
+        <v>34.2</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>6.04</v>
+      </c>
+      <c r="K19">
+        <v>0.207</v>
+      </c>
+      <c r="L19">
+        <v>5.833</v>
+      </c>
+      <c r="M19">
+        <v>0.4319564000000001</v>
+      </c>
+      <c r="N19">
+        <v>5.4010436</v>
+      </c>
+      <c r="O19">
+        <v>0.819950639478335</v>
+      </c>
+      <c r="P19">
+        <v>4.581092960521666</v>
+      </c>
+      <c r="Q19">
+        <v>4.788092960521666</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.08889919857860901</v>
+      </c>
+      <c r="T19">
+        <v>0.5949678851924602</v>
+      </c>
+      <c r="U19">
+        <v>0.0457</v>
+      </c>
+      <c r="V19">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W19">
+        <v>0.03876212891446389</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>13.50367768598868</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.08055499585529569</v>
+      </c>
+      <c r="C20">
+        <v>48.75206424022122</v>
+      </c>
+      <c r="D20">
+        <v>56.55006424022121</v>
+      </c>
+      <c r="E20">
+        <v>-11.392</v>
+      </c>
+      <c r="F20">
+        <v>10.008</v>
+      </c>
+      <c r="G20">
+        <v>2.21</v>
+      </c>
+      <c r="H20">
+        <v>34.2</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>6.04</v>
+      </c>
+      <c r="K20">
+        <v>0.207</v>
+      </c>
+      <c r="L20">
+        <v>5.833</v>
+      </c>
+      <c r="M20">
+        <v>0.4733784</v>
+      </c>
+      <c r="N20">
+        <v>5.359621600000001</v>
+      </c>
+      <c r="O20">
+        <v>0.8136622259968235</v>
+      </c>
+      <c r="P20">
+        <v>4.545959374003177</v>
+      </c>
+      <c r="Q20">
+        <v>4.752959374003177</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.08943114012406647</v>
+      </c>
+      <c r="T20">
+        <v>0.601285114715608</v>
+      </c>
+      <c r="U20">
+        <v>0.0473</v>
+      </c>
+      <c r="V20">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W20">
+        <v>0.04011922751978428</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>12.32206623707377</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.08050338821198255</v>
+      </c>
+      <c r="C21">
+        <v>48.23250841720508</v>
+      </c>
+      <c r="D21">
+        <v>56.58650841720507</v>
+      </c>
+      <c r="E21">
+        <v>-10.836</v>
+      </c>
+      <c r="F21">
+        <v>10.564</v>
+      </c>
+      <c r="G21">
+        <v>2.21</v>
+      </c>
+      <c r="H21">
+        <v>34.2</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>6.04</v>
+      </c>
+      <c r="K21">
+        <v>0.207</v>
+      </c>
+      <c r="L21">
+        <v>5.833</v>
+      </c>
+      <c r="M21">
+        <v>0.4996772</v>
+      </c>
+      <c r="N21">
+        <v>5.3333228</v>
+      </c>
+      <c r="O21">
+        <v>0.8096697164978235</v>
+      </c>
+      <c r="P21">
+        <v>4.523653083502177</v>
+      </c>
+      <c r="Q21">
+        <v>4.730653083502177</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.08997621602867102</v>
+      </c>
+      <c r="T21">
+        <v>0.6077583252146359</v>
+      </c>
+      <c r="U21">
+        <v>0.0473</v>
+      </c>
+      <c r="V21">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W21">
+        <v>0.04011922751978428</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>11.67353643512251</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.0804517805686694</v>
+      </c>
+      <c r="C22">
+        <v>47.71299959800976</v>
+      </c>
+      <c r="D22">
+        <v>56.62299959800976</v>
+      </c>
+      <c r="E22">
+        <v>-10.28</v>
+      </c>
+      <c r="F22">
+        <v>11.12</v>
+      </c>
+      <c r="G22">
+        <v>2.21</v>
+      </c>
+      <c r="H22">
+        <v>34.2</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>6.04</v>
+      </c>
+      <c r="K22">
+        <v>0.207</v>
+      </c>
+      <c r="L22">
+        <v>5.833</v>
+      </c>
+      <c r="M22">
+        <v>0.5259760000000001</v>
+      </c>
+      <c r="N22">
+        <v>5.307024</v>
+      </c>
+      <c r="O22">
+        <v>0.8056772069988235</v>
+      </c>
+      <c r="P22">
+        <v>4.501346793001177</v>
+      </c>
+      <c r="Q22">
+        <v>4.708346793001176</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.09053491883089068</v>
+      </c>
+      <c r="T22">
+        <v>0.6143933659761396</v>
+      </c>
+      <c r="U22">
+        <v>0.0473</v>
+      </c>
+      <c r="V22">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W22">
+        <v>0.04011922751978428</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>11.08985961336639</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.08040017292535627</v>
+      </c>
+      <c r="C23">
+        <v>47.19353787362861</v>
+      </c>
+      <c r="D23">
+        <v>56.65953787362861</v>
+      </c>
+      <c r="E23">
+        <v>-9.723999999999998</v>
+      </c>
+      <c r="F23">
+        <v>11.676</v>
+      </c>
+      <c r="G23">
+        <v>2.21</v>
+      </c>
+      <c r="H23">
+        <v>34.2</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>6.04</v>
+      </c>
+      <c r="K23">
+        <v>0.207</v>
+      </c>
+      <c r="L23">
+        <v>5.833</v>
+      </c>
+      <c r="M23">
+        <v>0.5522748000000001</v>
+      </c>
+      <c r="N23">
+        <v>5.2807252</v>
+      </c>
+      <c r="O23">
+        <v>0.8016846974998235</v>
+      </c>
+      <c r="P23">
+        <v>4.479040502500176</v>
+      </c>
+      <c r="Q23">
+        <v>4.686040502500176</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.09110776600785009</v>
+      </c>
+      <c r="T23">
+        <v>0.6211963824531243</v>
+      </c>
+      <c r="U23">
+        <v>0.0473</v>
+      </c>
+      <c r="V23">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W23">
+        <v>0.04011922751978428</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>10.56177106034894</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.08105764930332304</v>
+      </c>
+      <c r="C24">
+        <v>46.17554144524638</v>
+      </c>
+      <c r="D24">
+        <v>56.19754144524638</v>
+      </c>
+      <c r="E24">
+        <v>-9.167999999999997</v>
+      </c>
+      <c r="F24">
+        <v>12.232</v>
+      </c>
+      <c r="G24">
+        <v>2.21</v>
+      </c>
+      <c r="H24">
+        <v>34.2</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>6.04</v>
+      </c>
+      <c r="K24">
+        <v>0.207</v>
+      </c>
+      <c r="L24">
+        <v>5.833</v>
+      </c>
+      <c r="M24">
+        <v>0.6250552</v>
+      </c>
+      <c r="N24">
+        <v>5.2079448</v>
+      </c>
+      <c r="O24">
+        <v>0.7906356595839865</v>
+      </c>
+      <c r="P24">
+        <v>4.417309140416013</v>
+      </c>
+      <c r="Q24">
+        <v>4.624309140416013</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.0916953015739623</v>
+      </c>
+      <c r="T24">
+        <v>0.6281738352500317</v>
+      </c>
+      <c r="U24">
+        <v>0.0511</v>
+      </c>
+      <c r="V24">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W24">
+        <v>0.04334233670742023</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>9.331975799897352</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.08103827275188627</v>
+      </c>
+      <c r="C25">
+        <v>45.63304921388537</v>
+      </c>
+      <c r="D25">
+        <v>56.21104921388537</v>
+      </c>
+      <c r="E25">
+        <v>-8.611999999999998</v>
+      </c>
+      <c r="F25">
+        <v>12.788</v>
+      </c>
+      <c r="G25">
+        <v>2.21</v>
+      </c>
+      <c r="H25">
+        <v>34.2</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>6.04</v>
+      </c>
+      <c r="K25">
+        <v>0.207</v>
+      </c>
+      <c r="L25">
+        <v>5.833</v>
+      </c>
+      <c r="M25">
+        <v>0.6534668</v>
+      </c>
+      <c r="N25">
+        <v>5.1795332</v>
+      </c>
+      <c r="O25">
+        <v>0.7863223987933121</v>
+      </c>
+      <c r="P25">
+        <v>4.393210801206687</v>
+      </c>
+      <c r="Q25">
+        <v>4.600210801206687</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.09229809780412937</v>
+      </c>
+      <c r="T25">
+        <v>0.6353325205871186</v>
+      </c>
+      <c r="U25">
+        <v>0.0511</v>
+      </c>
+      <c r="V25">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W25">
+        <v>0.04334233670742023</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>8.926237721640945</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.0810188962004495</v>
+      </c>
+      <c r="C26">
+        <v>45.09056347760141</v>
+      </c>
+      <c r="D26">
+        <v>56.22456347760141</v>
+      </c>
+      <c r="E26">
+        <v>-8.055999999999999</v>
+      </c>
+      <c r="F26">
+        <v>13.344</v>
+      </c>
+      <c r="G26">
+        <v>2.21</v>
+      </c>
+      <c r="H26">
+        <v>34.2</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>6.04</v>
+      </c>
+      <c r="K26">
+        <v>0.207</v>
+      </c>
+      <c r="L26">
+        <v>5.833</v>
+      </c>
+      <c r="M26">
+        <v>0.6818784</v>
+      </c>
+      <c r="N26">
+        <v>5.1511216</v>
+      </c>
+      <c r="O26">
+        <v>0.7820091380026377</v>
+      </c>
+      <c r="P26">
+        <v>4.369112461997362</v>
+      </c>
+      <c r="Q26">
+        <v>4.576112461997362</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.09291675709298505</v>
+      </c>
+      <c r="T26">
+        <v>0.6426795923804446</v>
+      </c>
+      <c r="U26">
+        <v>0.0511</v>
+      </c>
+      <c r="V26">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W26">
+        <v>0.04334233670742023</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>8.554311149905907</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.08099951964901274</v>
+      </c>
+      <c r="C27">
+        <v>44.54808424108023</v>
+      </c>
+      <c r="D27">
+        <v>56.23808424108023</v>
+      </c>
+      <c r="E27">
+        <v>-7.499999999999998</v>
+      </c>
+      <c r="F27">
+        <v>13.9</v>
+      </c>
+      <c r="G27">
+        <v>2.21</v>
+      </c>
+      <c r="H27">
+        <v>34.2</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>6.04</v>
+      </c>
+      <c r="K27">
+        <v>0.207</v>
+      </c>
+      <c r="L27">
+        <v>5.833</v>
+      </c>
+      <c r="M27">
+        <v>0.71029</v>
+      </c>
+      <c r="N27">
+        <v>5.122710000000001</v>
+      </c>
+      <c r="O27">
+        <v>0.7776958772119635</v>
+      </c>
+      <c r="P27">
+        <v>4.345014122788037</v>
+      </c>
+      <c r="Q27">
+        <v>4.552014122788036</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.0935519139628769</v>
+      </c>
+      <c r="T27">
+        <v>0.6502225860882593</v>
+      </c>
+      <c r="U27">
+        <v>0.0511</v>
+      </c>
+      <c r="V27">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W27">
+        <v>0.04334233670742023</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>8.212138703909671</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.08098014309757594</v>
+      </c>
+      <c r="C28">
+        <v>44.00561150901216</v>
+      </c>
+      <c r="D28">
+        <v>56.25161150901216</v>
+      </c>
+      <c r="E28">
+        <v>-6.943999999999997</v>
+      </c>
+      <c r="F28">
+        <v>14.456</v>
+      </c>
+      <c r="G28">
+        <v>2.21</v>
+      </c>
+      <c r="H28">
+        <v>34.2</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>6.04</v>
+      </c>
+      <c r="K28">
+        <v>0.207</v>
+      </c>
+      <c r="L28">
+        <v>5.833</v>
+      </c>
+      <c r="M28">
+        <v>0.7387016000000001</v>
+      </c>
+      <c r="N28">
+        <v>5.0942984</v>
+      </c>
+      <c r="O28">
+        <v>0.7733826164212891</v>
+      </c>
+      <c r="P28">
+        <v>4.320915783578712</v>
+      </c>
+      <c r="Q28">
+        <v>4.527915783578711</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.09420423723465768</v>
+      </c>
+      <c r="T28">
+        <v>0.6579694444908797</v>
+      </c>
+      <c r="U28">
+        <v>0.0511</v>
+      </c>
+      <c r="V28">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W28">
+        <v>0.04334233670742023</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>7.89628721529776</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.08139588628647003</v>
+      </c>
+      <c r="C29">
+        <v>43.16079128572537</v>
+      </c>
+      <c r="D29">
+        <v>55.96279128572537</v>
+      </c>
+      <c r="E29">
+        <v>-6.387999999999996</v>
+      </c>
+      <c r="F29">
+        <v>15.012</v>
+      </c>
+      <c r="G29">
+        <v>2.21</v>
+      </c>
+      <c r="H29">
+        <v>34.2</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>6.04</v>
+      </c>
+      <c r="K29">
+        <v>0.207</v>
+      </c>
+      <c r="L29">
+        <v>5.833</v>
+      </c>
+      <c r="M29">
+        <v>0.7956360000000002</v>
+      </c>
+      <c r="N29">
+        <v>5.037364</v>
+      </c>
+      <c r="O29">
+        <v>0.7647392131930102</v>
+      </c>
+      <c r="P29">
+        <v>4.27262478680699</v>
+      </c>
+      <c r="Q29">
+        <v>4.47962478680699</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.09487443237689823</v>
+      </c>
+      <c r="T29">
+        <v>0.6659285455894624</v>
+      </c>
+      <c r="U29">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V29">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W29">
+        <v>0.0449538913012382</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>7.331241924699233</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.08139262528097144</v>
+      </c>
+      <c r="C30">
+        <v>42.60704519213004</v>
+      </c>
+      <c r="D30">
+        <v>55.96504519213005</v>
+      </c>
+      <c r="E30">
+        <v>-5.831999999999997</v>
+      </c>
+      <c r="F30">
+        <v>15.568</v>
+      </c>
+      <c r="G30">
+        <v>2.21</v>
+      </c>
+      <c r="H30">
+        <v>34.2</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>6.04</v>
+      </c>
+      <c r="K30">
+        <v>0.207</v>
+      </c>
+      <c r="L30">
+        <v>5.833</v>
+      </c>
+      <c r="M30">
+        <v>0.8251040000000002</v>
+      </c>
+      <c r="N30">
+        <v>5.007896</v>
+      </c>
+      <c r="O30">
+        <v>0.7602655767564985</v>
+      </c>
+      <c r="P30">
+        <v>4.247630423243502</v>
+      </c>
+      <c r="Q30">
+        <v>4.454630423243501</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.09556324405086769</v>
+      </c>
+      <c r="T30">
+        <v>0.6741087328296724</v>
+      </c>
+      <c r="U30">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V30">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W30">
+        <v>0.0449538913012382</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>7.069411855959975</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.08138936427547283</v>
+      </c>
+      <c r="C31">
+        <v>42.05329928009461</v>
+      </c>
+      <c r="D31">
+        <v>55.9672992800946</v>
+      </c>
+      <c r="E31">
+        <v>-5.276</v>
+      </c>
+      <c r="F31">
+        <v>16.124</v>
+      </c>
+      <c r="G31">
+        <v>2.21</v>
+      </c>
+      <c r="H31">
+        <v>34.2</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>6.04</v>
+      </c>
+      <c r="K31">
+        <v>0.207</v>
+      </c>
+      <c r="L31">
+        <v>5.833</v>
+      </c>
+      <c r="M31">
+        <v>0.854572</v>
+      </c>
+      <c r="N31">
+        <v>4.978428</v>
+      </c>
+      <c r="O31">
+        <v>0.7557919403199871</v>
+      </c>
+      <c r="P31">
+        <v>4.222636059680013</v>
+      </c>
+      <c r="Q31">
+        <v>4.429636059680013</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.09627145887058276</v>
+      </c>
+      <c r="T31">
+        <v>0.6825193478794658</v>
+      </c>
+      <c r="U31">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V31">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W31">
+        <v>0.0449538913012382</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>6.825639033340667</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.08138610326997424</v>
+      </c>
+      <c r="C32">
+        <v>41.49955354964096</v>
+      </c>
+      <c r="D32">
+        <v>55.96955354964096</v>
+      </c>
+      <c r="E32">
+        <v>-4.719999999999999</v>
+      </c>
+      <c r="F32">
+        <v>16.68</v>
+      </c>
+      <c r="G32">
+        <v>2.21</v>
+      </c>
+      <c r="H32">
+        <v>34.2</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>6.04</v>
+      </c>
+      <c r="K32">
+        <v>0.207</v>
+      </c>
+      <c r="L32">
+        <v>5.833</v>
+      </c>
+      <c r="M32">
+        <v>0.88404</v>
+      </c>
+      <c r="N32">
+        <v>4.94896</v>
+      </c>
+      <c r="O32">
+        <v>0.7513183038834755</v>
+      </c>
+      <c r="P32">
+        <v>4.197641696116525</v>
+      </c>
+      <c r="Q32">
+        <v>4.404641696116525</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.09699990839943254</v>
+      </c>
+      <c r="T32">
+        <v>0.6911702662163961</v>
+      </c>
+      <c r="U32">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V32">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W32">
+        <v>0.0449538913012382</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>6.598117732229311</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.08138284226447565</v>
+      </c>
+      <c r="C33">
+        <v>40.94580800079109</v>
+      </c>
+      <c r="D33">
+        <v>55.97180800079109</v>
+      </c>
+      <c r="E33">
+        <v>-4.163999999999998</v>
+      </c>
+      <c r="F33">
+        <v>17.236</v>
+      </c>
+      <c r="G33">
+        <v>2.21</v>
+      </c>
+      <c r="H33">
+        <v>34.2</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>6.04</v>
+      </c>
+      <c r="K33">
+        <v>0.207</v>
+      </c>
+      <c r="L33">
+        <v>5.833</v>
+      </c>
+      <c r="M33">
+        <v>0.9135080000000001</v>
+      </c>
+      <c r="N33">
+        <v>4.919492</v>
+      </c>
+      <c r="O33">
+        <v>0.7468446674469639</v>
+      </c>
+      <c r="P33">
+        <v>4.172647332553036</v>
+      </c>
+      <c r="Q33">
+        <v>4.379647332553036</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.09774947240737944</v>
+      </c>
+      <c r="T33">
+        <v>0.7000719358094694</v>
+      </c>
+      <c r="U33">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V33">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W33">
+        <v>0.0449538913012382</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>6.385275224738042</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.0819224207011052</v>
+      </c>
+      <c r="C34">
+        <v>40.01923270727742</v>
+      </c>
+      <c r="D34">
+        <v>55.60123270727742</v>
+      </c>
+      <c r="E34">
+        <v>-3.607999999999997</v>
+      </c>
+      <c r="F34">
+        <v>17.792</v>
+      </c>
+      <c r="G34">
+        <v>2.21</v>
+      </c>
+      <c r="H34">
+        <v>34.2</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>6.04</v>
+      </c>
+      <c r="K34">
+        <v>0.207</v>
+      </c>
+      <c r="L34">
+        <v>5.833</v>
+      </c>
+      <c r="M34">
+        <v>0.9785600000000001</v>
+      </c>
+      <c r="N34">
+        <v>4.85444</v>
+      </c>
+      <c r="O34">
+        <v>0.736968903992778</v>
+      </c>
+      <c r="P34">
+        <v>4.117471096007222</v>
+      </c>
+      <c r="Q34">
+        <v>4.324471096007222</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.09852108241556004</v>
+      </c>
+      <c r="T34">
+        <v>0.7092354192141035</v>
+      </c>
+      <c r="U34">
+        <v>0.055</v>
+      </c>
+      <c r="V34">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W34">
+        <v>0.0466502645578887</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>5.960799542184434</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.08193612342817312</v>
+      </c>
+      <c r="C35">
+        <v>39.45388573502177</v>
+      </c>
+      <c r="D35">
+        <v>55.59188573502177</v>
+      </c>
+      <c r="E35">
+        <v>-3.051999999999996</v>
+      </c>
+      <c r="F35">
+        <v>18.348</v>
+      </c>
+      <c r="G35">
+        <v>2.21</v>
+      </c>
+      <c r="H35">
+        <v>34.2</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>6.04</v>
+      </c>
+      <c r="K35">
+        <v>0.207</v>
+      </c>
+      <c r="L35">
+        <v>5.833</v>
+      </c>
+      <c r="M35">
+        <v>1.00914</v>
+      </c>
+      <c r="N35">
+        <v>4.82386</v>
+      </c>
+      <c r="O35">
+        <v>0.7323264510869641</v>
+      </c>
+      <c r="P35">
+        <v>4.091533548913036</v>
+      </c>
+      <c r="Q35">
+        <v>4.298533548913036</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.09931572555831322</v>
+      </c>
+      <c r="T35">
+        <v>0.7186724394367865</v>
+      </c>
+      <c r="U35">
+        <v>0.055</v>
+      </c>
+      <c r="V35">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W35">
+        <v>0.0466502645578887</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>5.78016925302733</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.08194982615524105</v>
+      </c>
+      <c r="C36">
+        <v>38.88854190482616</v>
+      </c>
+      <c r="D36">
+        <v>55.58254190482617</v>
+      </c>
+      <c r="E36">
+        <v>-2.495999999999995</v>
+      </c>
+      <c r="F36">
+        <v>18.904</v>
+      </c>
+      <c r="G36">
+        <v>2.21</v>
+      </c>
+      <c r="H36">
+        <v>34.2</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>6.04</v>
+      </c>
+      <c r="K36">
+        <v>0.207</v>
+      </c>
+      <c r="L36">
+        <v>5.833</v>
+      </c>
+      <c r="M36">
+        <v>1.03972</v>
+      </c>
+      <c r="N36">
+        <v>4.79328</v>
+      </c>
+      <c r="O36">
+        <v>0.7276839981811503</v>
+      </c>
+      <c r="P36">
+        <v>4.06559600181885</v>
+      </c>
+      <c r="Q36">
+        <v>4.27259600181885</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1001344487963013</v>
+      </c>
+      <c r="T36">
+        <v>0.7283954299692479</v>
+      </c>
+      <c r="U36">
+        <v>0.055</v>
+      </c>
+      <c r="V36">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W36">
+        <v>0.0466502645578887</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>5.610164274997114</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.08196352888230894</v>
+      </c>
+      <c r="C37">
+        <v>38.32320121510655</v>
+      </c>
+      <c r="D37">
+        <v>55.57320121510655</v>
+      </c>
+      <c r="E37">
+        <v>-1.939999999999998</v>
+      </c>
+      <c r="F37">
+        <v>19.46</v>
+      </c>
+      <c r="G37">
+        <v>2.21</v>
+      </c>
+      <c r="H37">
+        <v>34.2</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>6.04</v>
+      </c>
+      <c r="K37">
+        <v>0.207</v>
+      </c>
+      <c r="L37">
+        <v>5.833</v>
+      </c>
+      <c r="M37">
+        <v>1.0703</v>
+      </c>
+      <c r="N37">
+        <v>4.762700000000001</v>
+      </c>
+      <c r="O37">
+        <v>0.7230415452753365</v>
+      </c>
+      <c r="P37">
+        <v>4.039658454724664</v>
+      </c>
+      <c r="Q37">
+        <v>4.246658454724664</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1009783635185352</v>
+      </c>
+      <c r="T37">
+        <v>0.7384175894411694</v>
+      </c>
+      <c r="U37">
+        <v>0.055</v>
+      </c>
+      <c r="V37">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W37">
+        <v>0.0466502645578887</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>5.449873867140055</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.08197723160937685</v>
+      </c>
+      <c r="C38">
+        <v>37.75786366427988</v>
+      </c>
+      <c r="D38">
+        <v>55.56386366427988</v>
+      </c>
+      <c r="E38">
+        <v>-1.384</v>
+      </c>
+      <c r="F38">
+        <v>20.016</v>
+      </c>
+      <c r="G38">
+        <v>2.21</v>
+      </c>
+      <c r="H38">
+        <v>34.2</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>6.04</v>
+      </c>
+      <c r="K38">
+        <v>0.207</v>
+      </c>
+      <c r="L38">
+        <v>5.833</v>
+      </c>
+      <c r="M38">
+        <v>1.10088</v>
+      </c>
+      <c r="N38">
+        <v>4.73212</v>
+      </c>
+      <c r="O38">
+        <v>0.7183990923695225</v>
+      </c>
+      <c r="P38">
+        <v>4.013720907630478</v>
+      </c>
+      <c r="Q38">
+        <v>4.220720907630477</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1018486505758389</v>
+      </c>
+      <c r="T38">
+        <v>0.7487529413965885</v>
+      </c>
+      <c r="U38">
+        <v>0.055</v>
+      </c>
+      <c r="V38">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W38">
+        <v>0.0466502645578887</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>5.29848848194172</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.08199093433644476</v>
+      </c>
+      <c r="C39">
+        <v>37.19252925076424</v>
+      </c>
+      <c r="D39">
+        <v>55.55452925076423</v>
+      </c>
+      <c r="E39">
+        <v>-0.8279999999999994</v>
+      </c>
+      <c r="F39">
+        <v>20.572</v>
+      </c>
+      <c r="G39">
+        <v>2.21</v>
+      </c>
+      <c r="H39">
+        <v>34.2</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>6.04</v>
+      </c>
+      <c r="K39">
+        <v>0.207</v>
+      </c>
+      <c r="L39">
+        <v>5.833</v>
+      </c>
+      <c r="M39">
+        <v>1.13146</v>
+      </c>
+      <c r="N39">
+        <v>4.70154</v>
+      </c>
+      <c r="O39">
+        <v>0.7137566394637087</v>
+      </c>
+      <c r="P39">
+        <v>3.987783360536292</v>
+      </c>
+      <c r="Q39">
+        <v>4.194783360536292</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.102746565793692</v>
+      </c>
+      <c r="T39">
+        <v>0.7594163997632908</v>
+      </c>
+      <c r="U39">
+        <v>0.055</v>
+      </c>
+      <c r="V39">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W39">
+        <v>0.0466502645578887</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>5.155286090537889</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.08200463706351267</v>
+      </c>
+      <c r="C40">
+        <v>36.6271979729787</v>
+      </c>
+      <c r="D40">
+        <v>55.5451979729787</v>
+      </c>
+      <c r="E40">
+        <v>-0.2719999999999985</v>
+      </c>
+      <c r="F40">
+        <v>21.128</v>
+      </c>
+      <c r="G40">
+        <v>2.21</v>
+      </c>
+      <c r="H40">
+        <v>34.2</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>6.04</v>
+      </c>
+      <c r="K40">
+        <v>0.207</v>
+      </c>
+      <c r="L40">
+        <v>5.833</v>
+      </c>
+      <c r="M40">
+        <v>1.16204</v>
+      </c>
+      <c r="N40">
+        <v>4.67096</v>
+      </c>
+      <c r="O40">
+        <v>0.7091141865578947</v>
+      </c>
+      <c r="P40">
+        <v>3.961845813442105</v>
+      </c>
+      <c r="Q40">
+        <v>4.168845813442105</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1036734460185725</v>
+      </c>
+      <c r="T40">
+        <v>0.7704238406579512</v>
+      </c>
+      <c r="U40">
+        <v>0.055</v>
+      </c>
+      <c r="V40">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W40">
+        <v>0.0466502645578887</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>5.019620667102681</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.08201833979058058</v>
+      </c>
+      <c r="C41">
+        <v>36.06186982934346</v>
+      </c>
+      <c r="D41">
+        <v>55.53586982934347</v>
+      </c>
+      <c r="E41">
+        <v>0.2840000000000025</v>
+      </c>
+      <c r="F41">
+        <v>21.684</v>
+      </c>
+      <c r="G41">
+        <v>2.21</v>
+      </c>
+      <c r="H41">
+        <v>34.2</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>6.04</v>
+      </c>
+      <c r="K41">
+        <v>0.207</v>
+      </c>
+      <c r="L41">
+        <v>5.833</v>
+      </c>
+      <c r="M41">
+        <v>1.19262</v>
+      </c>
+      <c r="N41">
+        <v>4.64038</v>
+      </c>
+      <c r="O41">
+        <v>0.7044717336520809</v>
+      </c>
+      <c r="P41">
+        <v>3.935908266347919</v>
+      </c>
+      <c r="Q41">
+        <v>4.142908266347919</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1046307157590229</v>
+      </c>
+      <c r="T41">
+        <v>0.7817921812540759</v>
+      </c>
+      <c r="U41">
+        <v>0.055</v>
+      </c>
+      <c r="V41">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W41">
+        <v>0.0466502645578887</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>4.890912444869279</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.08203204251764849</v>
+      </c>
+      <c r="C42">
+        <v>35.49654481827978</v>
+      </c>
+      <c r="D42">
+        <v>55.52654481827978</v>
+      </c>
+      <c r="E42">
+        <v>0.8400000000000034</v>
+      </c>
+      <c r="F42">
+        <v>22.24</v>
+      </c>
+      <c r="G42">
+        <v>2.21</v>
+      </c>
+      <c r="H42">
+        <v>34.2</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>6.04</v>
+      </c>
+      <c r="K42">
+        <v>0.207</v>
+      </c>
+      <c r="L42">
+        <v>5.833</v>
+      </c>
+      <c r="M42">
+        <v>1.2232</v>
+      </c>
+      <c r="N42">
+        <v>4.6098</v>
+      </c>
+      <c r="O42">
+        <v>0.6998292807462669</v>
+      </c>
+      <c r="P42">
+        <v>3.909970719253733</v>
+      </c>
+      <c r="Q42">
+        <v>4.116970719253733</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1056198944908217</v>
+      </c>
+      <c r="T42">
+        <v>0.7935394665367381</v>
+      </c>
+      <c r="U42">
+        <v>0.055</v>
+      </c>
+      <c r="V42">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W42">
+        <v>0.0466502645578887</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>4.768639633747547</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.08204574524471642</v>
+      </c>
+      <c r="C43">
+        <v>34.93122293820991</v>
+      </c>
+      <c r="D43">
+        <v>55.51722293820992</v>
+      </c>
+      <c r="E43">
+        <v>1.396000000000004</v>
+      </c>
+      <c r="F43">
+        <v>22.796</v>
+      </c>
+      <c r="G43">
+        <v>2.21</v>
+      </c>
+      <c r="H43">
+        <v>34.2</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>6.04</v>
+      </c>
+      <c r="K43">
+        <v>0.207</v>
+      </c>
+      <c r="L43">
+        <v>5.833</v>
+      </c>
+      <c r="M43">
+        <v>1.25378</v>
+      </c>
+      <c r="N43">
+        <v>4.57922</v>
+      </c>
+      <c r="O43">
+        <v>0.695186827840453</v>
+      </c>
+      <c r="P43">
+        <v>3.884033172159547</v>
+      </c>
+      <c r="Q43">
+        <v>4.091033172159547</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1066426047050543</v>
+      </c>
+      <c r="T43">
+        <v>0.8056849648798295</v>
+      </c>
+      <c r="U43">
+        <v>0.055</v>
+      </c>
+      <c r="V43">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W43">
+        <v>0.0466502645578887</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>4.652331349997607</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.08205944797178431</v>
+      </c>
+      <c r="C44">
+        <v>34.36590418755726</v>
+      </c>
+      <c r="D44">
+        <v>55.50790418755726</v>
+      </c>
+      <c r="E44">
+        <v>1.952000000000002</v>
+      </c>
+      <c r="F44">
+        <v>23.352</v>
+      </c>
+      <c r="G44">
+        <v>2.21</v>
+      </c>
+      <c r="H44">
+        <v>34.2</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>6.04</v>
+      </c>
+      <c r="K44">
+        <v>0.207</v>
+      </c>
+      <c r="L44">
+        <v>5.833</v>
+      </c>
+      <c r="M44">
+        <v>1.28436</v>
+      </c>
+      <c r="N44">
+        <v>4.548640000000001</v>
+      </c>
+      <c r="O44">
+        <v>0.6905443749346393</v>
+      </c>
+      <c r="P44">
+        <v>3.858095625065361</v>
+      </c>
+      <c r="Q44">
+        <v>4.065095625065362</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1077005807887432</v>
+      </c>
+      <c r="T44">
+        <v>0.8182492735106137</v>
+      </c>
+      <c r="U44">
+        <v>0.055</v>
+      </c>
+      <c r="V44">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W44">
+        <v>0.0466502645578887</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>4.541561555950046</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.08345908764953569</v>
+      </c>
+      <c r="C45">
+        <v>32.87425912939399</v>
+      </c>
+      <c r="D45">
+        <v>54.57225912939399</v>
+      </c>
+      <c r="E45">
+        <v>2.508000000000003</v>
+      </c>
+      <c r="F45">
+        <v>23.908</v>
+      </c>
+      <c r="G45">
+        <v>2.21</v>
+      </c>
+      <c r="H45">
+        <v>34.2</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>6.04</v>
+      </c>
+      <c r="K45">
+        <v>0.207</v>
+      </c>
+      <c r="L45">
+        <v>5.833</v>
+      </c>
+      <c r="M45">
+        <v>1.4057904</v>
+      </c>
+      <c r="N45">
+        <v>4.4272096</v>
+      </c>
+      <c r="O45">
+        <v>0.6721096164868255</v>
+      </c>
+      <c r="P45">
+        <v>3.755099983513175</v>
+      </c>
+      <c r="Q45">
+        <v>3.962099983513175</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1087956788402809</v>
+      </c>
+      <c r="T45">
+        <v>0.8312544350758114</v>
+      </c>
+      <c r="U45">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V45">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W45">
+        <v>0.04987337374552465</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>4.149267202279942</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.08350502146847996</v>
+      </c>
+      <c r="C46">
+        <v>32.28808711130553</v>
+      </c>
+      <c r="D46">
+        <v>54.54208711130553</v>
+      </c>
+      <c r="E46">
+        <v>3.064000000000004</v>
+      </c>
+      <c r="F46">
+        <v>24.464</v>
+      </c>
+      <c r="G46">
+        <v>2.21</v>
+      </c>
+      <c r="H46">
+        <v>34.2</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>6.04</v>
+      </c>
+      <c r="K46">
+        <v>0.207</v>
+      </c>
+      <c r="L46">
+        <v>5.833</v>
+      </c>
+      <c r="M46">
+        <v>1.4384832</v>
+      </c>
+      <c r="N46">
+        <v>4.3945168</v>
+      </c>
+      <c r="O46">
+        <v>0.6671464122893371</v>
+      </c>
+      <c r="P46">
+        <v>3.727370387710663</v>
+      </c>
+      <c r="Q46">
+        <v>3.934370387710663</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1099298875365163</v>
+      </c>
+      <c r="T46">
+        <v>0.8447240666969091</v>
+      </c>
+      <c r="U46">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V46">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W46">
+        <v>0.04987337374552465</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>4.054965674955397</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.08515402801495894</v>
+      </c>
+      <c r="C47">
+        <v>30.67059089769153</v>
+      </c>
+      <c r="D47">
+        <v>53.48059089769153</v>
+      </c>
+      <c r="E47">
+        <v>3.620000000000001</v>
+      </c>
+      <c r="F47">
+        <v>25.02</v>
+      </c>
+      <c r="G47">
+        <v>2.21</v>
+      </c>
+      <c r="H47">
+        <v>34.2</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>6.04</v>
+      </c>
+      <c r="K47">
+        <v>0.207</v>
+      </c>
+      <c r="L47">
+        <v>5.833</v>
+      </c>
+      <c r="M47">
+        <v>1.57626</v>
+      </c>
+      <c r="N47">
+        <v>4.256740000000001</v>
+      </c>
+      <c r="O47">
+        <v>0.6462300517427795</v>
+      </c>
+      <c r="P47">
+        <v>3.610509948257221</v>
+      </c>
+      <c r="Q47">
+        <v>3.817509948257221</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1111053401853421</v>
+      </c>
+      <c r="T47">
+        <v>0.8586835031042285</v>
+      </c>
+      <c r="U47">
+        <v>0.063</v>
+      </c>
+      <c r="V47">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W47">
+        <v>0.05343575758449069</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>3.700531638181519</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.08523558567229288</v>
+      </c>
+      <c r="C48">
+        <v>30.06316197560243</v>
+      </c>
+      <c r="D48">
+        <v>53.42916197560243</v>
+      </c>
+      <c r="E48">
+        <v>4.176000000000002</v>
+      </c>
+      <c r="F48">
+        <v>25.576</v>
+      </c>
+      <c r="G48">
+        <v>2.21</v>
+      </c>
+      <c r="H48">
+        <v>34.2</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>6.04</v>
+      </c>
+      <c r="K48">
+        <v>0.207</v>
+      </c>
+      <c r="L48">
+        <v>5.833</v>
+      </c>
+      <c r="M48">
+        <v>1.611288</v>
+      </c>
+      <c r="N48">
+        <v>4.221712</v>
+      </c>
+      <c r="O48">
+        <v>0.6409123329597562</v>
+      </c>
+      <c r="P48">
+        <v>3.580799667040244</v>
+      </c>
+      <c r="Q48">
+        <v>3.787799667040244</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1123243281174577</v>
+      </c>
+      <c r="T48">
+        <v>0.8731599556747819</v>
+      </c>
+      <c r="U48">
+        <v>0.063</v>
+      </c>
+      <c r="V48">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W48">
+        <v>0.05343575758449069</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>3.620085298221051</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.08531714332962681</v>
+      </c>
+      <c r="C49">
+        <v>29.45583187040971</v>
+      </c>
+      <c r="D49">
+        <v>53.37783187040971</v>
+      </c>
+      <c r="E49">
+        <v>4.732000000000003</v>
+      </c>
+      <c r="F49">
+        <v>26.132</v>
+      </c>
+      <c r="G49">
+        <v>2.21</v>
+      </c>
+      <c r="H49">
+        <v>34.2</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>6.04</v>
+      </c>
+      <c r="K49">
+        <v>0.207</v>
+      </c>
+      <c r="L49">
+        <v>5.833</v>
+      </c>
+      <c r="M49">
+        <v>1.646316</v>
+      </c>
+      <c r="N49">
+        <v>4.186684</v>
+      </c>
+      <c r="O49">
+        <v>0.6355946141767329</v>
+      </c>
+      <c r="P49">
+        <v>3.551089385823267</v>
+      </c>
+      <c r="Q49">
+        <v>3.758089385823267</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1135893155941815</v>
+      </c>
+      <c r="T49">
+        <v>0.8881826894744128</v>
+      </c>
+      <c r="U49">
+        <v>0.063</v>
+      </c>
+      <c r="V49">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W49">
+        <v>0.05343575758449069</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>3.543062206769538</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.08828932101629318</v>
+      </c>
+      <c r="C50">
+        <v>27.09423910395005</v>
+      </c>
+      <c r="D50">
+        <v>51.57223910395005</v>
+      </c>
+      <c r="E50">
+        <v>5.288</v>
+      </c>
+      <c r="F50">
+        <v>26.688</v>
+      </c>
+      <c r="G50">
+        <v>2.21</v>
+      </c>
+      <c r="H50">
+        <v>34.2</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>6.04</v>
+      </c>
+      <c r="K50">
+        <v>0.207</v>
+      </c>
+      <c r="L50">
+        <v>5.833</v>
+      </c>
+      <c r="M50">
+        <v>1.8708288</v>
+      </c>
+      <c r="N50">
+        <v>3.9621712</v>
+      </c>
+      <c r="O50">
+        <v>0.601510569024594</v>
+      </c>
+      <c r="P50">
+        <v>3.360660630975406</v>
+      </c>
+      <c r="Q50">
+        <v>3.567660630975406</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1149029564353946</v>
+      </c>
+      <c r="T50">
+        <v>0.9037832207278756</v>
+      </c>
+      <c r="U50">
+        <v>0.0701</v>
+      </c>
+      <c r="V50">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W50">
+        <v>0.05945788264559995</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>3.117869470472125</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.0884310999242382</v>
+      </c>
+      <c r="C51">
+        <v>26.45515623033709</v>
+      </c>
+      <c r="D51">
+        <v>51.48915623033709</v>
+      </c>
+      <c r="E51">
+        <v>5.844000000000001</v>
+      </c>
+      <c r="F51">
+        <v>27.244</v>
+      </c>
+      <c r="G51">
+        <v>2.21</v>
+      </c>
+      <c r="H51">
+        <v>34.2</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>6.04</v>
+      </c>
+      <c r="K51">
+        <v>0.207</v>
+      </c>
+      <c r="L51">
+        <v>5.833</v>
+      </c>
+      <c r="M51">
+        <v>1.9098044</v>
+      </c>
+      <c r="N51">
+        <v>3.923195600000001</v>
+      </c>
+      <c r="O51">
+        <v>0.5955935517755476</v>
+      </c>
+      <c r="P51">
+        <v>3.327602048224453</v>
+      </c>
+      <c r="Q51">
+        <v>3.534602048224453</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1162681126037142</v>
+      </c>
+      <c r="T51">
+        <v>0.9199955375206901</v>
+      </c>
+      <c r="U51">
+        <v>0.0701</v>
+      </c>
+      <c r="V51">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W51">
+        <v>0.05945788264559995</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>3.054239481278816</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.09760606642384714</v>
+      </c>
+      <c r="C52">
+        <v>21.03804469210712</v>
+      </c>
+      <c r="D52">
+        <v>46.62804469210712</v>
+      </c>
+      <c r="E52">
+        <v>6.400000000000002</v>
+      </c>
+      <c r="F52">
+        <v>27.8</v>
+      </c>
+      <c r="G52">
+        <v>2.21</v>
+      </c>
+      <c r="H52">
+        <v>34.2</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>6.04</v>
+      </c>
+      <c r="K52">
+        <v>0.207</v>
+      </c>
+      <c r="L52">
+        <v>5.833</v>
+      </c>
+      <c r="M52">
+        <v>2.54092</v>
+      </c>
+      <c r="N52">
+        <v>3.29208</v>
+      </c>
+      <c r="O52">
+        <v>0.4997817646230141</v>
+      </c>
+      <c r="P52">
+        <v>2.792298235376986</v>
+      </c>
+      <c r="Q52">
+        <v>2.999298235376985</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1176878750187665</v>
+      </c>
+      <c r="T52">
+        <v>0.936856346985217</v>
+      </c>
+      <c r="U52">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V52">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W52">
+        <v>0.07752425782892777</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>2.295625206618075</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.09792850908362544</v>
+      </c>
+      <c r="C53">
+        <v>20.3278475063669</v>
+      </c>
+      <c r="D53">
+        <v>46.4738475063669</v>
+      </c>
+      <c r="E53">
+        <v>6.956000000000003</v>
+      </c>
+      <c r="F53">
+        <v>28.356</v>
+      </c>
+      <c r="G53">
+        <v>2.21</v>
+      </c>
+      <c r="H53">
+        <v>34.2</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>6.04</v>
+      </c>
+      <c r="K53">
+        <v>0.207</v>
+      </c>
+      <c r="L53">
+        <v>5.833</v>
+      </c>
+      <c r="M53">
+        <v>2.591738400000001</v>
+      </c>
+      <c r="N53">
+        <v>3.2412616</v>
+      </c>
+      <c r="O53">
+        <v>0.4920668519758979</v>
+      </c>
+      <c r="P53">
+        <v>2.749194748024102</v>
+      </c>
+      <c r="Q53">
+        <v>2.956194748024102</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1191655869201475</v>
+      </c>
+      <c r="T53">
+        <v>0.9544053527544185</v>
+      </c>
+      <c r="U53">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V53">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W53">
+        <v>0.07752425782892777</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>2.250612947664779</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.09825095174340374</v>
+      </c>
+      <c r="C54">
+        <v>19.61866680770107</v>
+      </c>
+      <c r="D54">
+        <v>46.32066680770107</v>
+      </c>
+      <c r="E54">
+        <v>7.512000000000004</v>
+      </c>
+      <c r="F54">
+        <v>28.912</v>
+      </c>
+      <c r="G54">
+        <v>2.21</v>
+      </c>
+      <c r="H54">
+        <v>34.2</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>6.04</v>
+      </c>
+      <c r="K54">
+        <v>0.207</v>
+      </c>
+      <c r="L54">
+        <v>5.833</v>
+      </c>
+      <c r="M54">
+        <v>2.6425568</v>
+      </c>
+      <c r="N54">
+        <v>3.1904432</v>
+      </c>
+      <c r="O54">
+        <v>0.4843519393287817</v>
+      </c>
+      <c r="P54">
+        <v>2.706091260671218</v>
+      </c>
+      <c r="Q54">
+        <v>2.913091260671218</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1207048701507527</v>
+      </c>
+      <c r="T54">
+        <v>0.9726855670973369</v>
+      </c>
+      <c r="U54">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V54">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W54">
+        <v>0.07752425782892777</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>2.207331929440457</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.09857339440318204</v>
+      </c>
+      <c r="C55">
+        <v>18.91049257791594</v>
+      </c>
+      <c r="D55">
+        <v>46.16849257791594</v>
+      </c>
+      <c r="E55">
+        <v>8.068000000000005</v>
+      </c>
+      <c r="F55">
+        <v>29.468</v>
+      </c>
+      <c r="G55">
+        <v>2.21</v>
+      </c>
+      <c r="H55">
+        <v>34.2</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>6.04</v>
+      </c>
+      <c r="K55">
+        <v>0.207</v>
+      </c>
+      <c r="L55">
+        <v>5.833</v>
+      </c>
+      <c r="M55">
+        <v>2.693375200000001</v>
+      </c>
+      <c r="N55">
+        <v>3.1396248</v>
+      </c>
+      <c r="O55">
+        <v>0.4766370266816656</v>
+      </c>
+      <c r="P55">
+        <v>2.662987773318334</v>
+      </c>
+      <c r="Q55">
+        <v>2.869987773318334</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1223096547954262</v>
+      </c>
+      <c r="T55">
+        <v>0.9917436629016557</v>
+      </c>
+      <c r="U55">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V55">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W55">
+        <v>0.07752425782892777</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>2.165684157186863</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.09889583706296033</v>
+      </c>
+      <c r="C56">
+        <v>18.20331493003515</v>
+      </c>
+      <c r="D56">
+        <v>46.01731493003516</v>
+      </c>
+      <c r="E56">
+        <v>8.624000000000006</v>
+      </c>
+      <c r="F56">
+        <v>30.024</v>
+      </c>
+      <c r="G56">
+        <v>2.21</v>
+      </c>
+      <c r="H56">
+        <v>34.2</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>6.04</v>
+      </c>
+      <c r="K56">
+        <v>0.207</v>
+      </c>
+      <c r="L56">
+        <v>5.833</v>
+      </c>
+      <c r="M56">
+        <v>2.744193600000001</v>
+      </c>
+      <c r="N56">
+        <v>3.088806399999999</v>
+      </c>
+      <c r="O56">
+        <v>0.4689221140345494</v>
+      </c>
+      <c r="P56">
+        <v>2.61988428596545</v>
+      </c>
+      <c r="Q56">
+        <v>2.82688428596545</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1239842126855203</v>
+      </c>
+      <c r="T56">
+        <v>1.011630371567032</v>
+      </c>
+      <c r="U56">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V56">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W56">
+        <v>0.07752425782892777</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>2.125578895016736</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.09921827972273864</v>
+      </c>
+      <c r="C57">
+        <v>17.49712410615839</v>
+      </c>
+      <c r="D57">
+        <v>45.86712410615839</v>
+      </c>
+      <c r="E57">
+        <v>9.180000000000003</v>
+      </c>
+      <c r="F57">
+        <v>30.58</v>
+      </c>
+      <c r="G57">
+        <v>2.21</v>
+      </c>
+      <c r="H57">
+        <v>34.2</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>6.04</v>
+      </c>
+      <c r="K57">
+        <v>0.207</v>
+      </c>
+      <c r="L57">
+        <v>5.833</v>
+      </c>
+      <c r="M57">
+        <v>2.795012</v>
+      </c>
+      <c r="N57">
+        <v>3.037988</v>
+      </c>
+      <c r="O57">
+        <v>0.4612072013874333</v>
+      </c>
+      <c r="P57">
+        <v>2.576780798612567</v>
+      </c>
+      <c r="Q57">
+        <v>2.783780798612566</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1257331953707297</v>
+      </c>
+      <c r="T57">
+        <v>1.03240093395087</v>
+      </c>
+      <c r="U57">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V57">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W57">
+        <v>0.07752425782892777</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>2.086932006016432</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.09954072238251695</v>
+      </c>
+      <c r="C58">
+        <v>16.79191047536185</v>
+      </c>
+      <c r="D58">
+        <v>45.71791047536185</v>
+      </c>
+      <c r="E58">
+        <v>9.736000000000004</v>
+      </c>
+      <c r="F58">
+        <v>31.136</v>
+      </c>
+      <c r="G58">
+        <v>2.21</v>
+      </c>
+      <c r="H58">
+        <v>34.2</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>6.04</v>
+      </c>
+      <c r="K58">
+        <v>0.207</v>
+      </c>
+      <c r="L58">
+        <v>5.833</v>
+      </c>
+      <c r="M58">
+        <v>2.845830400000001</v>
+      </c>
+      <c r="N58">
+        <v>2.9871696</v>
+      </c>
+      <c r="O58">
+        <v>0.4534922887403171</v>
+      </c>
+      <c r="P58">
+        <v>2.533677311259682</v>
+      </c>
+      <c r="Q58">
+        <v>2.740677311259682</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1275616772689032</v>
+      </c>
+      <c r="T58">
+        <v>1.0541156128067</v>
+      </c>
+      <c r="U58">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V58">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W58">
+        <v>0.07752425782892777</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>2.049665363051853</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.09986316504229525</v>
+      </c>
+      <c r="C59">
+        <v>16.08766453163951</v>
+      </c>
+      <c r="D59">
+        <v>45.56966453163951</v>
+      </c>
+      <c r="E59">
+        <v>10.29200000000001</v>
+      </c>
+      <c r="F59">
+        <v>31.692</v>
+      </c>
+      <c r="G59">
+        <v>2.21</v>
+      </c>
+      <c r="H59">
+        <v>34.2</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>6.04</v>
+      </c>
+      <c r="K59">
+        <v>0.207</v>
+      </c>
+      <c r="L59">
+        <v>5.833</v>
+      </c>
+      <c r="M59">
+        <v>2.896648800000001</v>
+      </c>
+      <c r="N59">
+        <v>2.936351199999999</v>
+      </c>
+      <c r="O59">
+        <v>0.4457773760932009</v>
+      </c>
+      <c r="P59">
+        <v>2.490573823906798</v>
+      </c>
+      <c r="Q59">
+        <v>2.697573823906798</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1294752048367591</v>
+      </c>
+      <c r="T59">
+        <v>1.076840276725592</v>
+      </c>
+      <c r="U59">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V59">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W59">
+        <v>0.07752425782892777</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>2.013706321594802</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1105657156595179</v>
+      </c>
+      <c r="C60">
+        <v>11.10361401147193</v>
+      </c>
+      <c r="D60">
+        <v>41.14161401147193</v>
+      </c>
+      <c r="E60">
+        <v>10.848</v>
+      </c>
+      <c r="F60">
+        <v>32.248</v>
+      </c>
+      <c r="G60">
+        <v>2.21</v>
+      </c>
+      <c r="H60">
+        <v>34.2</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>6.04</v>
+      </c>
+      <c r="K60">
+        <v>0.207</v>
+      </c>
+      <c r="L60">
+        <v>5.833</v>
+      </c>
+      <c r="M60">
+        <v>3.6279</v>
+      </c>
+      <c r="N60">
+        <v>2.2051</v>
+      </c>
+      <c r="O60">
+        <v>0.3347636658799933</v>
+      </c>
+      <c r="P60">
+        <v>1.870336334120007</v>
+      </c>
+      <c r="Q60">
+        <v>2.077336334120007</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1314798527649891</v>
+      </c>
+      <c r="T60">
+        <v>1.100647067497764</v>
+      </c>
+      <c r="U60">
+        <v>0.1125</v>
+      </c>
+      <c r="V60">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W60">
+        <v>0.09542099568659052</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>1.607817194520246</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1110671256978729</v>
+      </c>
+      <c r="C61">
+        <v>10.36116881875239</v>
+      </c>
+      <c r="D61">
+        <v>40.95516881875239</v>
+      </c>
+      <c r="E61">
+        <v>11.404</v>
+      </c>
+      <c r="F61">
+        <v>32.804</v>
+      </c>
+      <c r="G61">
+        <v>2.21</v>
+      </c>
+      <c r="H61">
+        <v>34.2</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>6.04</v>
+      </c>
+      <c r="K61">
+        <v>0.207</v>
+      </c>
+      <c r="L61">
+        <v>5.833</v>
+      </c>
+      <c r="M61">
+        <v>3.69045</v>
+      </c>
+      <c r="N61">
+        <v>2.14255</v>
+      </c>
+      <c r="O61">
+        <v>0.3252677394817376</v>
+      </c>
+      <c r="P61">
+        <v>1.817282260518262</v>
+      </c>
+      <c r="Q61">
+        <v>2.024282260518262</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1335822883970353</v>
+      </c>
+      <c r="T61">
+        <v>1.125615165136872</v>
+      </c>
+      <c r="U61">
+        <v>0.1125</v>
+      </c>
+      <c r="V61">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W61">
+        <v>0.09542099568659052</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>1.580566055630072</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1115685357362278</v>
+      </c>
+      <c r="C62">
+        <v>9.620405863745319</v>
+      </c>
+      <c r="D62">
+        <v>40.77040586374532</v>
+      </c>
+      <c r="E62">
+        <v>11.96</v>
+      </c>
+      <c r="F62">
+        <v>33.36</v>
+      </c>
+      <c r="G62">
+        <v>2.21</v>
+      </c>
+      <c r="H62">
+        <v>34.2</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>6.04</v>
+      </c>
+      <c r="K62">
+        <v>0.207</v>
+      </c>
+      <c r="L62">
+        <v>5.833</v>
+      </c>
+      <c r="M62">
+        <v>3.753</v>
+      </c>
+      <c r="N62">
+        <v>2.08</v>
+      </c>
+      <c r="O62">
+        <v>0.315771813083482</v>
+      </c>
+      <c r="P62">
+        <v>1.764228186916518</v>
+      </c>
+      <c r="Q62">
+        <v>1.971228186916518</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1357898458106837</v>
+      </c>
+      <c r="T62">
+        <v>1.151831667657935</v>
+      </c>
+      <c r="U62">
+        <v>0.1125</v>
+      </c>
+      <c r="V62">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W62">
+        <v>0.09542099568659052</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>1.554223288036238</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1120699457745827</v>
+      </c>
+      <c r="C63">
+        <v>8.881302481230037</v>
+      </c>
+      <c r="D63">
+        <v>40.58730248123003</v>
+      </c>
+      <c r="E63">
+        <v>12.516</v>
+      </c>
+      <c r="F63">
+        <v>33.916</v>
+      </c>
+      <c r="G63">
+        <v>2.21</v>
+      </c>
+      <c r="H63">
+        <v>34.2</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>6.04</v>
+      </c>
+      <c r="K63">
+        <v>0.207</v>
+      </c>
+      <c r="L63">
+        <v>5.833</v>
+      </c>
+      <c r="M63">
+        <v>3.81555</v>
+      </c>
+      <c r="N63">
+        <v>2.017450000000001</v>
+      </c>
+      <c r="O63">
+        <v>0.3062758866852264</v>
+      </c>
+      <c r="P63">
+        <v>1.711174113314774</v>
+      </c>
+      <c r="Q63">
+        <v>1.918174113314774</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1381106112968269</v>
+      </c>
+      <c r="T63">
+        <v>1.17939260620572</v>
+      </c>
+      <c r="U63">
+        <v>0.1125</v>
+      </c>
+      <c r="V63">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W63">
+        <v>0.09542099568659052</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>1.528744217740562</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1125713558129376</v>
+      </c>
+      <c r="C64">
+        <v>8.143836411331215</v>
+      </c>
+      <c r="D64">
+        <v>40.40583641133122</v>
+      </c>
+      <c r="E64">
+        <v>13.072</v>
+      </c>
+      <c r="F64">
+        <v>34.472</v>
+      </c>
+      <c r="G64">
+        <v>2.21</v>
+      </c>
+      <c r="H64">
+        <v>34.2</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>6.04</v>
+      </c>
+      <c r="K64">
+        <v>0.207</v>
+      </c>
+      <c r="L64">
+        <v>5.833</v>
+      </c>
+      <c r="M64">
+        <v>3.8781</v>
+      </c>
+      <c r="N64">
+        <v>1.9549</v>
+      </c>
+      <c r="O64">
+        <v>0.2967799602869706</v>
+      </c>
+      <c r="P64">
+        <v>1.658120039713029</v>
+      </c>
+      <c r="Q64">
+        <v>1.865120039713029</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1405535223348724</v>
+      </c>
+      <c r="T64">
+        <v>1.208404120466545</v>
+      </c>
+      <c r="U64">
+        <v>0.1125</v>
+      </c>
+      <c r="V64">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W64">
+        <v>0.09542099568659052</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>1.504087052938294</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.161513315916115</v>
+      </c>
+      <c r="C65">
+        <v>-4.688240463596692</v>
+      </c>
+      <c r="D65">
+        <v>28.12975953640331</v>
+      </c>
+      <c r="E65">
+        <v>13.628</v>
+      </c>
+      <c r="F65">
+        <v>35.028</v>
+      </c>
+      <c r="G65">
+        <v>2.21</v>
+      </c>
+      <c r="H65">
+        <v>34.2</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>6.04</v>
+      </c>
+      <c r="K65">
+        <v>0.207</v>
+      </c>
+      <c r="L65">
+        <v>5.833</v>
+      </c>
+      <c r="M65">
+        <v>6.8865048</v>
+      </c>
+      <c r="N65">
+        <v>-1.0535048</v>
+      </c>
+      <c r="O65">
+        <v>-0.1599361157635341</v>
+      </c>
+      <c r="P65">
+        <v>-0.8935686842364656</v>
+      </c>
+      <c r="Q65">
+        <v>-0.6865686842364657</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1448163990819956</v>
+      </c>
+      <c r="T65">
+        <v>1.259029177054874</v>
+      </c>
+      <c r="U65">
+        <v>0.1966</v>
+      </c>
+      <c r="V65">
+        <v>0.1285888012419337</v>
+      </c>
+      <c r="W65">
+        <v>0.1713194416758358</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.8470189405807138</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.163091315916115</v>
+      </c>
+      <c r="C66">
+        <v>-5.517121644692594</v>
+      </c>
+      <c r="D66">
+        <v>27.85687835530741</v>
+      </c>
+      <c r="E66">
+        <v>14.184</v>
+      </c>
+      <c r="F66">
+        <v>35.584</v>
+      </c>
+      <c r="G66">
+        <v>2.21</v>
+      </c>
+      <c r="H66">
+        <v>34.2</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>6.04</v>
+      </c>
+      <c r="K66">
+        <v>0.207</v>
+      </c>
+      <c r="L66">
+        <v>5.833</v>
+      </c>
+      <c r="M66">
+        <v>6.9958144</v>
+      </c>
+      <c r="N66">
+        <v>-1.1628144</v>
+      </c>
+      <c r="O66">
+        <v>-0.1765307746959526</v>
+      </c>
+      <c r="P66">
+        <v>-0.9862836253040477</v>
+      </c>
+      <c r="Q66">
+        <v>-0.7792836253040477</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1477612990564955</v>
+      </c>
+      <c r="T66">
+        <v>1.294002209750843</v>
+      </c>
+      <c r="U66">
+        <v>0.1966</v>
+      </c>
+      <c r="V66">
+        <v>0.1265796012225285</v>
+      </c>
+      <c r="W66">
+        <v>0.1717144503996509</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.8337842696341401</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.164669315916115</v>
+      </c>
+      <c r="C67">
+        <v>-6.340759359891276</v>
+      </c>
+      <c r="D67">
+        <v>27.58924064010872</v>
+      </c>
+      <c r="E67">
+        <v>14.74</v>
+      </c>
+      <c r="F67">
+        <v>36.14</v>
+      </c>
+      <c r="G67">
+        <v>2.21</v>
+      </c>
+      <c r="H67">
+        <v>34.2</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>6.04</v>
+      </c>
+      <c r="K67">
+        <v>0.207</v>
+      </c>
+      <c r="L67">
+        <v>5.833</v>
+      </c>
+      <c r="M67">
+        <v>7.105124</v>
+      </c>
+      <c r="N67">
+        <v>-1.272124</v>
+      </c>
+      <c r="O67">
+        <v>-0.1931254336283708</v>
+      </c>
+      <c r="P67">
+        <v>-1.078998566371629</v>
+      </c>
+      <c r="Q67">
+        <v>-0.8719985663716291</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1508744790295383</v>
+      </c>
+      <c r="T67">
+        <v>1.33097370145801</v>
+      </c>
+      <c r="U67">
+        <v>0.1966</v>
+      </c>
+      <c r="V67">
+        <v>0.1246322227421819</v>
+      </c>
+      <c r="W67">
+        <v>0.172097305008887</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.8209568193320764</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.166247315916115</v>
+      </c>
+      <c r="C68">
+        <v>-7.159303302353248</v>
+      </c>
+      <c r="D68">
+        <v>27.32669669764676</v>
+      </c>
+      <c r="E68">
+        <v>15.29600000000001</v>
+      </c>
+      <c r="F68">
+        <v>36.69600000000001</v>
+      </c>
+      <c r="G68">
+        <v>2.21</v>
+      </c>
+      <c r="H68">
+        <v>34.2</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>6.04</v>
+      </c>
+      <c r="K68">
+        <v>0.207</v>
+      </c>
+      <c r="L68">
+        <v>5.833</v>
+      </c>
+      <c r="M68">
+        <v>7.2144336</v>
+      </c>
+      <c r="N68">
+        <v>-1.3814336</v>
+      </c>
+      <c r="O68">
+        <v>-0.2097200925607893</v>
+      </c>
+      <c r="P68">
+        <v>-1.171713507439211</v>
+      </c>
+      <c r="Q68">
+        <v>-0.9647135074392111</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1541707872362894</v>
+      </c>
+      <c r="T68">
+        <v>1.37011998679501</v>
+      </c>
+      <c r="U68">
+        <v>0.1966</v>
+      </c>
+      <c r="V68">
+        <v>0.1227438557309367</v>
+      </c>
+      <c r="W68">
+        <v>0.1724685579632979</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.8085180796452267</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1796274978212741</v>
+      </c>
+      <c r="C69">
+        <v>-9.755647607419757</v>
+      </c>
+      <c r="D69">
+        <v>25.28635239258024</v>
+      </c>
+      <c r="E69">
+        <v>15.852</v>
+      </c>
+      <c r="F69">
+        <v>37.252</v>
+      </c>
+      <c r="G69">
+        <v>2.21</v>
+      </c>
+      <c r="H69">
+        <v>34.2</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>6.04</v>
+      </c>
+      <c r="K69">
+        <v>0.207</v>
+      </c>
+      <c r="L69">
+        <v>5.833</v>
+      </c>
+      <c r="M69">
+        <v>7.9644776</v>
+      </c>
+      <c r="N69">
+        <v>-2.1314776</v>
+      </c>
+      <c r="O69">
+        <v>-0.3235868011052062</v>
+      </c>
+      <c r="P69">
+        <v>-1.807890798894794</v>
+      </c>
+      <c r="Q69">
+        <v>-1.600890798894794</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1585098471681742</v>
+      </c>
+      <c r="T69">
+        <v>1.421649779379339</v>
+      </c>
+      <c r="U69">
+        <v>0.2138</v>
+      </c>
+      <c r="V69">
+        <v>0.1111846176802384</v>
+      </c>
+      <c r="W69">
+        <v>0.190028728739965</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.7323769734753225</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.181377497821274</v>
+      </c>
+      <c r="C70">
+        <v>-10.55619218240078</v>
+      </c>
+      <c r="D70">
+        <v>25.04180781759922</v>
+      </c>
+      <c r="E70">
+        <v>16.40800000000001</v>
+      </c>
+      <c r="F70">
+        <v>37.80800000000001</v>
+      </c>
+      <c r="G70">
+        <v>2.21</v>
+      </c>
+      <c r="H70">
+        <v>34.2</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>6.04</v>
+      </c>
+      <c r="K70">
+        <v>0.207</v>
+      </c>
+      <c r="L70">
+        <v>5.833</v>
+      </c>
+      <c r="M70">
+        <v>8.0833504</v>
+      </c>
+      <c r="N70">
+        <v>-2.2503504</v>
+      </c>
+      <c r="O70">
+        <v>-0.3416332816736245</v>
+      </c>
+      <c r="P70">
+        <v>-1.908717118326376</v>
+      </c>
+      <c r="Q70">
+        <v>-1.701717118326376</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1622507798921796</v>
+      </c>
+      <c r="T70">
+        <v>1.466076334984943</v>
+      </c>
+      <c r="U70">
+        <v>0.2138</v>
+      </c>
+      <c r="V70">
+        <v>0.109549549773176</v>
+      </c>
+      <c r="W70">
+        <v>0.190378306258495</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.7216067238653913</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.183127497821274</v>
+      </c>
+      <c r="C71">
+        <v>-11.35205207675905</v>
+      </c>
+      <c r="D71">
+        <v>24.80194792324095</v>
+      </c>
+      <c r="E71">
+        <v>16.96400000000001</v>
+      </c>
+      <c r="F71">
+        <v>38.364</v>
+      </c>
+      <c r="G71">
+        <v>2.21</v>
+      </c>
+      <c r="H71">
+        <v>34.2</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>6.04</v>
+      </c>
+      <c r="K71">
+        <v>0.207</v>
+      </c>
+      <c r="L71">
+        <v>5.833</v>
+      </c>
+      <c r="M71">
+        <v>8.202223200000001</v>
+      </c>
+      <c r="N71">
+        <v>-2.3692232</v>
+      </c>
+      <c r="O71">
+        <v>-0.3596797622420429</v>
+      </c>
+      <c r="P71">
+        <v>-2.009543437757958</v>
+      </c>
+      <c r="Q71">
+        <v>-1.802543437757958</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.166233063114508</v>
+      </c>
+      <c r="T71">
+        <v>1.513369119984458</v>
+      </c>
+      <c r="U71">
+        <v>0.2138</v>
+      </c>
+      <c r="V71">
+        <v>0.1079618751387822</v>
+      </c>
+      <c r="W71">
+        <v>0.1907177510953283</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.711148655403574</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1848774978212741</v>
+      </c>
+      <c r="C72">
+        <v>-12.14336062825679</v>
+      </c>
+      <c r="D72">
+        <v>24.56663937174321</v>
+      </c>
+      <c r="E72">
+        <v>17.52</v>
+      </c>
+      <c r="F72">
+        <v>38.92</v>
+      </c>
+      <c r="G72">
+        <v>2.21</v>
+      </c>
+      <c r="H72">
+        <v>34.2</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>6.04</v>
+      </c>
+      <c r="K72">
+        <v>0.207</v>
+      </c>
+      <c r="L72">
+        <v>5.833</v>
+      </c>
+      <c r="M72">
+        <v>8.321096000000001</v>
+      </c>
+      <c r="N72">
+        <v>-2.488096000000001</v>
+      </c>
+      <c r="O72">
+        <v>-0.3777262428104612</v>
+      </c>
+      <c r="P72">
+        <v>-2.110369757189539</v>
+      </c>
+      <c r="Q72">
+        <v>-1.903369757189539</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1704808318849916</v>
+      </c>
+      <c r="T72">
+        <v>1.563814757317273</v>
+      </c>
+      <c r="U72">
+        <v>0.2138</v>
+      </c>
+      <c r="V72">
+        <v>0.1064195626367996</v>
+      </c>
+      <c r="W72">
+        <v>0.1910474975082523</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.7009893888978086</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.186627497821274</v>
+      </c>
+      <c r="C73">
+        <v>-12.9302461620438</v>
+      </c>
+      <c r="D73">
+        <v>24.3357538379562</v>
+      </c>
+      <c r="E73">
+        <v>18.076</v>
+      </c>
+      <c r="F73">
+        <v>39.476</v>
+      </c>
+      <c r="G73">
+        <v>2.21</v>
+      </c>
+      <c r="H73">
+        <v>34.2</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>6.04</v>
+      </c>
+      <c r="K73">
+        <v>0.207</v>
+      </c>
+      <c r="L73">
+        <v>5.833</v>
+      </c>
+      <c r="M73">
+        <v>8.439968799999999</v>
+      </c>
+      <c r="N73">
+        <v>-2.606968799999999</v>
+      </c>
+      <c r="O73">
+        <v>-0.3957727233788793</v>
+      </c>
+      <c r="P73">
+        <v>-2.211196076621119</v>
+      </c>
+      <c r="Q73">
+        <v>-2.00419607662112</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1750215502258533</v>
+      </c>
+      <c r="T73">
+        <v>1.617739404121317</v>
+      </c>
+      <c r="U73">
+        <v>0.2138</v>
+      </c>
+      <c r="V73">
+        <v>0.104920695557408</v>
+      </c>
+      <c r="W73">
+        <v>0.1913679552898262</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.6911162989133326</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.1883774978212741</v>
+      </c>
+      <c r="C74">
+        <v>-13.71283222401536</v>
+      </c>
+      <c r="D74">
+        <v>24.10916777598464</v>
+      </c>
+      <c r="E74">
+        <v>18.632</v>
+      </c>
+      <c r="F74">
+        <v>40.032</v>
+      </c>
+      <c r="G74">
+        <v>2.21</v>
+      </c>
+      <c r="H74">
+        <v>34.2</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>6.04</v>
+      </c>
+      <c r="K74">
+        <v>0.207</v>
+      </c>
+      <c r="L74">
+        <v>5.833</v>
+      </c>
+      <c r="M74">
+        <v>8.558841599999999</v>
+      </c>
+      <c r="N74">
+        <v>-2.725841599999999</v>
+      </c>
+      <c r="O74">
+        <v>-0.4138192039472977</v>
+      </c>
+      <c r="P74">
+        <v>-2.312022396052702</v>
+      </c>
+      <c r="Q74">
+        <v>-2.105022396052702</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1798866055910624</v>
+      </c>
+      <c r="T74">
+        <v>1.675515811411364</v>
+      </c>
+      <c r="U74">
+        <v>0.2138</v>
+      </c>
+      <c r="V74">
+        <v>0.1034634636746663</v>
+      </c>
+      <c r="W74">
+        <v>0.1916795114663563</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.6815174614284252</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.190127497821274</v>
+      </c>
+      <c r="C75">
+        <v>-14.49123780125387</v>
+      </c>
+      <c r="D75">
+        <v>23.88676219874613</v>
+      </c>
+      <c r="E75">
+        <v>19.188</v>
+      </c>
+      <c r="F75">
+        <v>40.588</v>
+      </c>
+      <c r="G75">
+        <v>2.21</v>
+      </c>
+      <c r="H75">
+        <v>34.2</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>6.04</v>
+      </c>
+      <c r="K75">
+        <v>0.207</v>
+      </c>
+      <c r="L75">
+        <v>5.833</v>
+      </c>
+      <c r="M75">
+        <v>8.677714399999999</v>
+      </c>
+      <c r="N75">
+        <v>-2.844714399999999</v>
+      </c>
+      <c r="O75">
+        <v>-0.431865684515716</v>
+      </c>
+      <c r="P75">
+        <v>-2.412848715484283</v>
+      </c>
+      <c r="Q75">
+        <v>-2.205848715484283</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.1851120354277684</v>
+      </c>
+      <c r="T75">
+        <v>1.737571952574747</v>
+      </c>
+      <c r="U75">
+        <v>0.2138</v>
+      </c>
+      <c r="V75">
+        <v>0.1020461559530955</v>
+      </c>
+      <c r="W75">
+        <v>0.1919825318572282</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.6721816057924193</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.191877497821274</v>
+      </c>
+      <c r="C76">
+        <v>-15.26557753038065</v>
+      </c>
+      <c r="D76">
+        <v>23.66842246961934</v>
+      </c>
+      <c r="E76">
+        <v>19.744</v>
+      </c>
+      <c r="F76">
+        <v>41.144</v>
+      </c>
+      <c r="G76">
+        <v>2.21</v>
+      </c>
+      <c r="H76">
+        <v>34.2</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>6.04</v>
+      </c>
+      <c r="K76">
+        <v>0.207</v>
+      </c>
+      <c r="L76">
+        <v>5.833</v>
+      </c>
+      <c r="M76">
+        <v>8.796587199999999</v>
+      </c>
+      <c r="N76">
+        <v>-2.963587199999999</v>
+      </c>
+      <c r="O76">
+        <v>-0.4499121650841343</v>
+      </c>
+      <c r="P76">
+        <v>-2.513675034915865</v>
+      </c>
+      <c r="Q76">
+        <v>-2.306675034915865</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.1907394214057595</v>
+      </c>
+      <c r="T76">
+        <v>1.804401643058392</v>
+      </c>
+      <c r="U76">
+        <v>0.2138</v>
+      </c>
+      <c r="V76">
+        <v>0.1006671538456212</v>
+      </c>
+      <c r="W76">
+        <v>0.1922773625078062</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.6630980705790083</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.193627497821274</v>
+      </c>
+      <c r="C77">
+        <v>-16.03596189458447</v>
+      </c>
+      <c r="D77">
+        <v>23.45403810541553</v>
+      </c>
+      <c r="E77">
+        <v>20.3</v>
+      </c>
+      <c r="F77">
+        <v>41.7</v>
+      </c>
+      <c r="G77">
+        <v>2.21</v>
+      </c>
+      <c r="H77">
+        <v>34.2</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>6.04</v>
+      </c>
+      <c r="K77">
+        <v>0.207</v>
+      </c>
+      <c r="L77">
+        <v>5.833</v>
+      </c>
+      <c r="M77">
+        <v>8.915459999999999</v>
+      </c>
+      <c r="N77">
+        <v>-3.082459999999999</v>
+      </c>
+      <c r="O77">
+        <v>-0.4679586456525527</v>
+      </c>
+      <c r="P77">
+        <v>-2.614501354347447</v>
+      </c>
+      <c r="Q77">
+        <v>-2.407501354347447</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.1968169982619899</v>
+      </c>
+      <c r="T77">
+        <v>1.876577708780727</v>
+      </c>
+      <c r="U77">
+        <v>0.2138</v>
+      </c>
+      <c r="V77">
+        <v>0.0993249251276796</v>
+      </c>
+      <c r="W77">
+        <v>0.1925643310077021</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.6542567629712881</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.195377497821274</v>
+      </c>
+      <c r="C78">
+        <v>-16.80249741003822</v>
+      </c>
+      <c r="D78">
+        <v>23.24350258996178</v>
+      </c>
+      <c r="E78">
+        <v>20.856</v>
+      </c>
+      <c r="F78">
+        <v>42.256</v>
+      </c>
+      <c r="G78">
+        <v>2.21</v>
+      </c>
+      <c r="H78">
+        <v>34.2</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>6.04</v>
+      </c>
+      <c r="K78">
+        <v>0.207</v>
+      </c>
+      <c r="L78">
+        <v>5.833</v>
+      </c>
+      <c r="M78">
+        <v>9.0343328</v>
+      </c>
+      <c r="N78">
+        <v>-3.201332799999999</v>
+      </c>
+      <c r="O78">
+        <v>-0.4860051262209711</v>
+      </c>
+      <c r="P78">
+        <v>-2.715327673779028</v>
+      </c>
+      <c r="Q78">
+        <v>-2.508327673779029</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2034010398562394</v>
+      </c>
+      <c r="T78">
+        <v>1.954768446646591</v>
+      </c>
+      <c r="U78">
+        <v>0.2138</v>
+      </c>
+      <c r="V78">
+        <v>0.09801801821810488</v>
+      </c>
+      <c r="W78">
+        <v>0.1928437477049692</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.6456481213532448</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.197127497821274</v>
+      </c>
+      <c r="C79">
+        <v>-17.56528680236485</v>
+      </c>
+      <c r="D79">
+        <v>23.03671319763515</v>
+      </c>
+      <c r="E79">
+        <v>21.41200000000001</v>
+      </c>
+      <c r="F79">
+        <v>42.812</v>
+      </c>
+      <c r="G79">
+        <v>2.21</v>
+      </c>
+      <c r="H79">
+        <v>34.2</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>6.04</v>
+      </c>
+      <c r="K79">
+        <v>0.207</v>
+      </c>
+      <c r="L79">
+        <v>5.833</v>
+      </c>
+      <c r="M79">
+        <v>9.1532056</v>
+      </c>
+      <c r="N79">
+        <v>-3.3202056</v>
+      </c>
+      <c r="O79">
+        <v>-0.5040516067893894</v>
+      </c>
+      <c r="P79">
+        <v>-2.81615399321061</v>
+      </c>
+      <c r="Q79">
+        <v>-2.60915399321061</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2105576068065108</v>
+      </c>
+      <c r="T79">
+        <v>2.039758379109486</v>
+      </c>
+      <c r="U79">
+        <v>0.2138</v>
+      </c>
+      <c r="V79">
+        <v>0.09674505694254507</v>
+      </c>
+      <c r="W79">
+        <v>0.1931159068256839</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.6372630808161897</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.1988774978212741</v>
+      </c>
+      <c r="C80">
+        <v>-18.32442917376644</v>
+      </c>
+      <c r="D80">
+        <v>22.83357082623356</v>
+      </c>
+      <c r="E80">
+        <v>21.968</v>
+      </c>
+      <c r="F80">
+        <v>43.368</v>
+      </c>
+      <c r="G80">
+        <v>2.21</v>
+      </c>
+      <c r="H80">
+        <v>34.2</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>6.04</v>
+      </c>
+      <c r="K80">
+        <v>0.207</v>
+      </c>
+      <c r="L80">
+        <v>5.833</v>
+      </c>
+      <c r="M80">
+        <v>9.2720784</v>
+      </c>
+      <c r="N80">
+        <v>-3.4390784</v>
+      </c>
+      <c r="O80">
+        <v>-0.5220980873578077</v>
+      </c>
+      <c r="P80">
+        <v>-2.916980312642192</v>
+      </c>
+      <c r="Q80">
+        <v>-2.709980312642192</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2183647707522613</v>
+      </c>
+      <c r="T80">
+        <v>2.132474669069009</v>
+      </c>
+      <c r="U80">
+        <v>0.2138</v>
+      </c>
+      <c r="V80">
+        <v>0.09550473569969192</v>
+      </c>
+      <c r="W80">
+        <v>0.1933810875074059</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.6290930413185463</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.200627497821274</v>
+      </c>
+      <c r="C81">
+        <v>-19.08002016138803</v>
+      </c>
+      <c r="D81">
+        <v>22.63397983861197</v>
+      </c>
+      <c r="E81">
+        <v>22.52400000000001</v>
+      </c>
+      <c r="F81">
+        <v>43.92400000000001</v>
+      </c>
+      <c r="G81">
+        <v>2.21</v>
+      </c>
+      <c r="H81">
+        <v>34.2</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>6.04</v>
+      </c>
+      <c r="K81">
+        <v>0.207</v>
+      </c>
+      <c r="L81">
+        <v>5.833</v>
+      </c>
+      <c r="M81">
+        <v>9.390951200000002</v>
+      </c>
+      <c r="N81">
+        <v>-3.557951200000002</v>
+      </c>
+      <c r="O81">
+        <v>-0.5401445679262263</v>
+      </c>
+      <c r="P81">
+        <v>-3.017806632073775</v>
+      </c>
+      <c r="Q81">
+        <v>-2.810806632073775</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2269154741214166</v>
+      </c>
+      <c r="T81">
+        <v>2.234021081881819</v>
+      </c>
+      <c r="U81">
+        <v>0.2138</v>
+      </c>
+      <c r="V81">
+        <v>0.09429581499463252</v>
+      </c>
+      <c r="W81">
+        <v>0.1936395547541476</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.621129838263881</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.202377497821274</v>
+      </c>
+      <c r="C82">
+        <v>-19.83215208744772</v>
+      </c>
+      <c r="D82">
+        <v>22.43784791255229</v>
+      </c>
+      <c r="E82">
+        <v>23.08000000000001</v>
+      </c>
+      <c r="F82">
+        <v>44.48</v>
+      </c>
+      <c r="G82">
+        <v>2.21</v>
+      </c>
+      <c r="H82">
+        <v>34.2</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>6.04</v>
+      </c>
+      <c r="K82">
+        <v>0.207</v>
+      </c>
+      <c r="L82">
+        <v>5.833</v>
+      </c>
+      <c r="M82">
+        <v>9.509824</v>
+      </c>
+      <c r="N82">
+        <v>-3.676824</v>
+      </c>
+      <c r="O82">
+        <v>-0.5581910484946445</v>
+      </c>
+      <c r="P82">
+        <v>-3.118632951505355</v>
+      </c>
+      <c r="Q82">
+        <v>-2.911632951505355</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2363212478274874</v>
+      </c>
+      <c r="T82">
+        <v>2.34572213597591</v>
+      </c>
+      <c r="U82">
+        <v>0.2138</v>
+      </c>
+      <c r="V82">
+        <v>0.09311711730719963</v>
+      </c>
+      <c r="W82">
+        <v>0.1938915603197207</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.6133657152855826</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.204127497821274</v>
+      </c>
+      <c r="C83">
+        <v>-20.58091410162818</v>
+      </c>
+      <c r="D83">
+        <v>22.24508589837182</v>
+      </c>
+      <c r="E83">
+        <v>23.636</v>
+      </c>
+      <c r="F83">
+        <v>45.036</v>
+      </c>
+      <c r="G83">
+        <v>2.21</v>
+      </c>
+      <c r="H83">
+        <v>34.2</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>6.04</v>
+      </c>
+      <c r="K83">
+        <v>0.207</v>
+      </c>
+      <c r="L83">
+        <v>5.833</v>
+      </c>
+      <c r="M83">
+        <v>9.6286968</v>
+      </c>
+      <c r="N83">
+        <v>-3.7956968</v>
+      </c>
+      <c r="O83">
+        <v>-0.5762375290630628</v>
+      </c>
+      <c r="P83">
+        <v>-3.219459270936937</v>
+      </c>
+      <c r="Q83">
+        <v>-3.012459270936938</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2467171029763025</v>
+      </c>
+      <c r="T83">
+        <v>2.469181195764115</v>
+      </c>
+      <c r="U83">
+        <v>0.2138</v>
+      </c>
+      <c r="V83">
+        <v>0.09196752326637</v>
+      </c>
+      <c r="W83">
+        <v>0.1941373435256501</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.605793299047489</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.205877497821274</v>
+      </c>
+      <c r="C84">
+        <v>-21.32639231619111</v>
+      </c>
+      <c r="D84">
+        <v>22.05560768380889</v>
+      </c>
+      <c r="E84">
+        <v>24.19200000000001</v>
+      </c>
+      <c r="F84">
+        <v>45.59200000000001</v>
+      </c>
+      <c r="G84">
+        <v>2.21</v>
+      </c>
+      <c r="H84">
+        <v>34.2</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>6.04</v>
+      </c>
+      <c r="K84">
+        <v>0.207</v>
+      </c>
+      <c r="L84">
+        <v>5.833</v>
+      </c>
+      <c r="M84">
+        <v>9.7475696</v>
+      </c>
+      <c r="N84">
+        <v>-3.9145696</v>
+      </c>
+      <c r="O84">
+        <v>-0.5942840096314812</v>
+      </c>
+      <c r="P84">
+        <v>-3.320285590368519</v>
+      </c>
+      <c r="Q84">
+        <v>-3.113285590368519</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2582680531416527</v>
+      </c>
+      <c r="T84">
+        <v>2.606357928862122</v>
+      </c>
+      <c r="U84">
+        <v>0.2138</v>
+      </c>
+      <c r="V84">
+        <v>0.09084596810458501</v>
+      </c>
+      <c r="W84">
+        <v>0.1943771320192397</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.5984055758883733</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.207627497821274</v>
+      </c>
+      <c r="C85">
+        <v>-22.06866993424473</v>
+      </c>
+      <c r="D85">
+        <v>21.86933006575527</v>
+      </c>
+      <c r="E85">
+        <v>24.748</v>
+      </c>
+      <c r="F85">
+        <v>46.148</v>
+      </c>
+      <c r="G85">
+        <v>2.21</v>
+      </c>
+      <c r="H85">
+        <v>34.2</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>6.04</v>
+      </c>
+      <c r="K85">
+        <v>0.207</v>
+      </c>
+      <c r="L85">
+        <v>5.833</v>
+      </c>
+      <c r="M85">
+        <v>9.8664424</v>
+      </c>
+      <c r="N85">
+        <v>-4.0334424</v>
+      </c>
+      <c r="O85">
+        <v>-0.6123304901998995</v>
+      </c>
+      <c r="P85">
+        <v>-3.421111909800101</v>
+      </c>
+      <c r="Q85">
+        <v>-3.214111909800101</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.2711779386205734</v>
+      </c>
+      <c r="T85">
+        <v>2.75967310114813</v>
+      </c>
+      <c r="U85">
+        <v>0.2138</v>
+      </c>
+      <c r="V85">
+        <v>0.08975143836838517</v>
+      </c>
+      <c r="W85">
+        <v>0.1946111424768392</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.5911958701547784</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.209377497821274</v>
+      </c>
+      <c r="C86">
+        <v>-22.80782737156574</v>
+      </c>
+      <c r="D86">
+        <v>21.68617262843426</v>
+      </c>
+      <c r="E86">
+        <v>25.304</v>
+      </c>
+      <c r="F86">
+        <v>46.704</v>
+      </c>
+      <c r="G86">
+        <v>2.21</v>
+      </c>
+      <c r="H86">
+        <v>34.2</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>6.04</v>
+      </c>
+      <c r="K86">
+        <v>0.207</v>
+      </c>
+      <c r="L86">
+        <v>5.833</v>
+      </c>
+      <c r="M86">
+        <v>9.985315200000001</v>
+      </c>
+      <c r="N86">
+        <v>-4.1523152</v>
+      </c>
+      <c r="O86">
+        <v>-0.6303769707683179</v>
+      </c>
+      <c r="P86">
+        <v>-3.521938229231683</v>
+      </c>
+      <c r="Q86">
+        <v>-3.314938229231683</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.2857015597843591</v>
+      </c>
+      <c r="T86">
+        <v>2.932152669969886</v>
+      </c>
+      <c r="U86">
+        <v>0.2138</v>
+      </c>
+      <c r="V86">
+        <v>0.08868296886399964</v>
+      </c>
+      <c r="W86">
+        <v>0.1948395812568769</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.5841578240815072</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.211127497821274</v>
+      </c>
+      <c r="C87">
+        <v>-23.54394237235063</v>
+      </c>
+      <c r="D87">
+        <v>21.50605762764937</v>
+      </c>
+      <c r="E87">
+        <v>25.86</v>
+      </c>
+      <c r="F87">
+        <v>47.26</v>
+      </c>
+      <c r="G87">
+        <v>2.21</v>
+      </c>
+      <c r="H87">
+        <v>34.2</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>6.04</v>
+      </c>
+      <c r="K87">
+        <v>0.207</v>
+      </c>
+      <c r="L87">
+        <v>5.833</v>
+      </c>
+      <c r="M87">
+        <v>10.104188</v>
+      </c>
+      <c r="N87">
+        <v>-4.271187999999999</v>
+      </c>
+      <c r="O87">
+        <v>-0.648423451336736</v>
+      </c>
+      <c r="P87">
+        <v>-3.622764548663262</v>
+      </c>
+      <c r="Q87">
+        <v>-3.415764548663263</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3021616637699831</v>
+      </c>
+      <c r="T87">
+        <v>3.127629514634545</v>
+      </c>
+      <c r="U87">
+        <v>0.2138</v>
+      </c>
+      <c r="V87">
+        <v>0.08763963981854084</v>
+      </c>
+      <c r="W87">
+        <v>0.195062645006796</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.5772853790923131</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.212877497821274</v>
+      </c>
+      <c r="C88">
+        <v>-24.27709011924608</v>
+      </c>
+      <c r="D88">
+        <v>21.32890988075392</v>
+      </c>
+      <c r="E88">
+        <v>26.416</v>
+      </c>
+      <c r="F88">
+        <v>47.816</v>
+      </c>
+      <c r="G88">
+        <v>2.21</v>
+      </c>
+      <c r="H88">
+        <v>34.2</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>6.04</v>
+      </c>
+      <c r="K88">
+        <v>0.207</v>
+      </c>
+      <c r="L88">
+        <v>5.833</v>
+      </c>
+      <c r="M88">
+        <v>10.2230608</v>
+      </c>
+      <c r="N88">
+        <v>-4.390060800000001</v>
+      </c>
+      <c r="O88">
+        <v>-0.6664699319051546</v>
+      </c>
+      <c r="P88">
+        <v>-3.723590868094846</v>
+      </c>
+      <c r="Q88">
+        <v>-3.516590868094846</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.3209732111821248</v>
+      </c>
+      <c r="T88">
+        <v>3.351031622822727</v>
+      </c>
+      <c r="U88">
+        <v>0.2138</v>
+      </c>
+      <c r="V88">
+        <v>0.08662057423925545</v>
+      </c>
+      <c r="W88">
+        <v>0.1952805212276472</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.5705727584051931</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.214627497821274</v>
+      </c>
+      <c r="C89">
+        <v>-25.00734333798592</v>
+      </c>
+      <c r="D89">
+        <v>21.15465666201408</v>
+      </c>
+      <c r="E89">
+        <v>26.972</v>
+      </c>
+      <c r="F89">
+        <v>48.372</v>
+      </c>
+      <c r="G89">
+        <v>2.21</v>
+      </c>
+      <c r="H89">
+        <v>34.2</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>6.04</v>
+      </c>
+      <c r="K89">
+        <v>0.207</v>
+      </c>
+      <c r="L89">
+        <v>5.833</v>
+      </c>
+      <c r="M89">
+        <v>10.3419336</v>
+      </c>
+      <c r="N89">
+        <v>-4.508933599999999</v>
+      </c>
+      <c r="O89">
+        <v>-0.6845164124735726</v>
+      </c>
+      <c r="P89">
+        <v>-3.824417187526426</v>
+      </c>
+      <c r="Q89">
+        <v>-3.617417187526426</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.3426788428115189</v>
+      </c>
+      <c r="T89">
+        <v>3.608803286116783</v>
+      </c>
+      <c r="U89">
+        <v>0.2138</v>
+      </c>
+      <c r="V89">
+        <v>0.08562493545489622</v>
+      </c>
+      <c r="W89">
+        <v>0.1954933887997432</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.5640144508373174</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2163774978212741</v>
+      </c>
+      <c r="C90">
+        <v>-25.73477239694047</v>
+      </c>
+      <c r="D90">
+        <v>20.98322760305953</v>
+      </c>
+      <c r="E90">
+        <v>27.52800000000001</v>
+      </c>
+      <c r="F90">
+        <v>48.928</v>
+      </c>
+      <c r="G90">
+        <v>2.21</v>
+      </c>
+      <c r="H90">
+        <v>34.2</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>6.04</v>
+      </c>
+      <c r="K90">
+        <v>0.207</v>
+      </c>
+      <c r="L90">
+        <v>5.833</v>
+      </c>
+      <c r="M90">
+        <v>10.4608064</v>
+      </c>
+      <c r="N90">
+        <v>-4.627806400000001</v>
+      </c>
+      <c r="O90">
+        <v>-0.7025628930419913</v>
+      </c>
+      <c r="P90">
+        <v>-3.925243506958009</v>
+      </c>
+      <c r="Q90">
+        <v>-3.71824350695801</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.3680020797124789</v>
+      </c>
+      <c r="T90">
+        <v>3.909536893293182</v>
+      </c>
+      <c r="U90">
+        <v>0.2138</v>
+      </c>
+      <c r="V90">
+        <v>0.08465192482472692</v>
+      </c>
+      <c r="W90">
+        <v>0.1957014184724734</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.5576051957141659</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.218127497821274</v>
+      </c>
+      <c r="C91">
+        <v>-26.45944540186441</v>
+      </c>
+      <c r="D91">
+        <v>20.81455459813559</v>
+      </c>
+      <c r="E91">
+        <v>28.084</v>
+      </c>
+      <c r="F91">
+        <v>49.484</v>
+      </c>
+      <c r="G91">
+        <v>2.21</v>
+      </c>
+      <c r="H91">
+        <v>34.2</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>6.04</v>
+      </c>
+      <c r="K91">
+        <v>0.207</v>
+      </c>
+      <c r="L91">
+        <v>5.833</v>
+      </c>
+      <c r="M91">
+        <v>10.5796792</v>
+      </c>
+      <c r="N91">
+        <v>-4.746679199999999</v>
+      </c>
+      <c r="O91">
+        <v>-0.7206093736104093</v>
+      </c>
+      <c r="P91">
+        <v>-4.026069826389589</v>
+      </c>
+      <c r="Q91">
+        <v>-3.819069826389589</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.3979295415045225</v>
+      </c>
+      <c r="T91">
+        <v>4.264949338138018</v>
+      </c>
+      <c r="U91">
+        <v>0.2138</v>
+      </c>
+      <c r="V91">
+        <v>0.08370077960197719</v>
+      </c>
+      <c r="W91">
+        <v>0.1959047733210973</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.5513399687960293</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2198774978212741</v>
+      </c>
+      <c r="C92">
+        <v>-27.18142828611151</v>
+      </c>
+      <c r="D92">
+        <v>20.64857171388849</v>
+      </c>
+      <c r="E92">
+        <v>28.64</v>
+      </c>
+      <c r="F92">
+        <v>50.04</v>
+      </c>
+      <c r="G92">
+        <v>2.21</v>
+      </c>
+      <c r="H92">
+        <v>34.2</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>6.04</v>
+      </c>
+      <c r="K92">
+        <v>0.207</v>
+      </c>
+      <c r="L92">
+        <v>5.833</v>
+      </c>
+      <c r="M92">
+        <v>10.698552</v>
+      </c>
+      <c r="N92">
+        <v>-4.865551999999999</v>
+      </c>
+      <c r="O92">
+        <v>-0.7386558541788277</v>
+      </c>
+      <c r="P92">
+        <v>-4.126896145821171</v>
+      </c>
+      <c r="Q92">
+        <v>-3.919896145821172</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.4338424956549747</v>
+      </c>
+      <c r="T92">
+        <v>4.691444271951819</v>
+      </c>
+      <c r="U92">
+        <v>0.2138</v>
+      </c>
+      <c r="V92">
+        <v>0.08277077093973301</v>
+      </c>
+      <c r="W92">
+        <v>0.1961036091730851</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.5452139691427401</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2216274978212741</v>
+      </c>
+      <c r="C93">
+        <v>-27.90078489656691</v>
+      </c>
+      <c r="D93">
+        <v>20.4852151034331</v>
+      </c>
+      <c r="E93">
+        <v>29.19600000000001</v>
+      </c>
+      <c r="F93">
+        <v>50.596</v>
+      </c>
+      <c r="G93">
+        <v>2.21</v>
+      </c>
+      <c r="H93">
+        <v>34.2</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>6.04</v>
+      </c>
+      <c r="K93">
+        <v>0.207</v>
+      </c>
+      <c r="L93">
+        <v>5.833</v>
+      </c>
+      <c r="M93">
+        <v>10.8174248</v>
+      </c>
+      <c r="N93">
+        <v>-4.984424799999999</v>
+      </c>
+      <c r="O93">
+        <v>-0.7567023347472461</v>
+      </c>
+      <c r="P93">
+        <v>-4.227722465252754</v>
+      </c>
+      <c r="Q93">
+        <v>-4.020722465252754</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.4777361062833053</v>
+      </c>
+      <c r="T93">
+        <v>5.212715857724244</v>
+      </c>
+      <c r="U93">
+        <v>0.2138</v>
+      </c>
+      <c r="V93">
+        <v>0.08186120202830736</v>
+      </c>
+      <c r="W93">
+        <v>0.1962980750063479</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.5392226068444682</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2233774978212741</v>
+      </c>
+      <c r="C94">
+        <v>-28.61757707553247</v>
+      </c>
+      <c r="D94">
+        <v>20.32442292446753</v>
+      </c>
+      <c r="E94">
+        <v>29.752</v>
+      </c>
+      <c r="F94">
+        <v>51.152</v>
+      </c>
+      <c r="G94">
+        <v>2.21</v>
+      </c>
+      <c r="H94">
+        <v>34.2</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>6.04</v>
+      </c>
+      <c r="K94">
+        <v>0.207</v>
+      </c>
+      <c r="L94">
+        <v>5.833</v>
+      </c>
+      <c r="M94">
+        <v>10.9362976</v>
+      </c>
+      <c r="N94">
+        <v>-5.103297599999999</v>
+      </c>
+      <c r="O94">
+        <v>-0.7747488153156644</v>
+      </c>
+      <c r="P94">
+        <v>-4.328548784684335</v>
+      </c>
+      <c r="Q94">
+        <v>-4.121548784684335</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.5326031195687186</v>
+      </c>
+      <c r="T94">
+        <v>5.864305339939777</v>
+      </c>
+      <c r="U94">
+        <v>0.2138</v>
+      </c>
+      <c r="V94">
+        <v>0.08097140635408663</v>
+      </c>
+      <c r="W94">
+        <v>0.1964883133214963</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.5333614915526805</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2251274978212741</v>
+      </c>
+      <c r="C95">
+        <v>-29.33186473878584</v>
+      </c>
+      <c r="D95">
+        <v>20.16613526121417</v>
+      </c>
+      <c r="E95">
+        <v>30.30800000000001</v>
+      </c>
+      <c r="F95">
+        <v>51.70800000000001</v>
+      </c>
+      <c r="G95">
+        <v>2.21</v>
+      </c>
+      <c r="H95">
+        <v>34.2</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>6.04</v>
+      </c>
+      <c r="K95">
+        <v>0.207</v>
+      </c>
+      <c r="L95">
+        <v>5.833</v>
+      </c>
+      <c r="M95">
+        <v>11.0551704</v>
+      </c>
+      <c r="N95">
+        <v>-5.222170400000001</v>
+      </c>
+      <c r="O95">
+        <v>-0.792795295884083</v>
+      </c>
+      <c r="P95">
+        <v>-4.429375104115918</v>
+      </c>
+      <c r="Q95">
+        <v>-4.222375104115918</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.60314642236425</v>
+      </c>
+      <c r="T95">
+        <v>6.702063245645459</v>
+      </c>
+      <c r="U95">
+        <v>0.2138</v>
+      </c>
+      <c r="V95">
+        <v>0.08010074607070934</v>
+      </c>
+      <c r="W95">
+        <v>0.1966744604900823</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.5276264217510387</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.226877497821274</v>
+      </c>
+      <c r="C96">
+        <v>-30.04370595001998</v>
+      </c>
+      <c r="D96">
+        <v>20.01029404998003</v>
+      </c>
+      <c r="E96">
+        <v>30.864</v>
+      </c>
+      <c r="F96">
+        <v>52.264</v>
+      </c>
+      <c r="G96">
+        <v>2.21</v>
+      </c>
+      <c r="H96">
+        <v>34.2</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>6.04</v>
+      </c>
+      <c r="K96">
+        <v>0.207</v>
+      </c>
+      <c r="L96">
+        <v>5.833</v>
+      </c>
+      <c r="M96">
+        <v>11.1740432</v>
+      </c>
+      <c r="N96">
+        <v>-5.3410432</v>
+      </c>
+      <c r="O96">
+        <v>-0.8108417764525011</v>
+      </c>
+      <c r="P96">
+        <v>-4.530201423547498</v>
+      </c>
+      <c r="Q96">
+        <v>-4.323201423547498</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.6972041594249583</v>
+      </c>
+      <c r="T96">
+        <v>7.819073786586371</v>
+      </c>
+      <c r="U96">
+        <v>0.2138</v>
+      </c>
+      <c r="V96">
+        <v>0.07924861047421246</v>
+      </c>
+      <c r="W96">
+        <v>0.1968566470806133</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.5220133747111342</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2286274978212741</v>
+      </c>
+      <c r="C97">
+        <v>-30.75315699185778</v>
+      </c>
+      <c r="D97">
+        <v>19.85684300814223</v>
+      </c>
+      <c r="E97">
+        <v>31.42000000000001</v>
+      </c>
+      <c r="F97">
+        <v>52.82000000000001</v>
+      </c>
+      <c r="G97">
+        <v>2.21</v>
+      </c>
+      <c r="H97">
+        <v>34.2</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>6.04</v>
+      </c>
+      <c r="K97">
+        <v>0.207</v>
+      </c>
+      <c r="L97">
+        <v>5.833</v>
+      </c>
+      <c r="M97">
+        <v>11.292916</v>
+      </c>
+      <c r="N97">
+        <v>-5.459916000000002</v>
+      </c>
+      <c r="O97">
+        <v>-0.8288882570209197</v>
+      </c>
+      <c r="P97">
+        <v>-4.631027742979082</v>
+      </c>
+      <c r="Q97">
+        <v>-4.424027742979082</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.8288849913099505</v>
+      </c>
+      <c r="T97">
+        <v>9.38288854390365</v>
+      </c>
+      <c r="U97">
+        <v>0.2138</v>
+      </c>
+      <c r="V97">
+        <v>0.07841441457448388</v>
+      </c>
+      <c r="W97">
+        <v>0.1970349981639754</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.5165184970825958</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.230377497821274</v>
+      </c>
+      <c r="C98">
+        <v>-31.46027243362385</v>
+      </c>
+      <c r="D98">
+        <v>19.70572756637615</v>
+      </c>
+      <c r="E98">
+        <v>31.976</v>
+      </c>
+      <c r="F98">
+        <v>53.376</v>
+      </c>
+      <c r="G98">
+        <v>2.21</v>
+      </c>
+      <c r="H98">
+        <v>34.2</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>6.04</v>
+      </c>
+      <c r="K98">
+        <v>0.207</v>
+      </c>
+      <c r="L98">
+        <v>5.833</v>
+      </c>
+      <c r="M98">
+        <v>11.4117888</v>
+      </c>
+      <c r="N98">
+        <v>-5.578788799999998</v>
+      </c>
+      <c r="O98">
+        <v>-0.8469347375893376</v>
+      </c>
+      <c r="P98">
+        <v>-4.731854062410661</v>
+      </c>
+      <c r="Q98">
+        <v>-4.524854062410661</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.026406239137436</v>
+      </c>
+      <c r="T98">
+        <v>11.72861067987954</v>
+      </c>
+      <c r="U98">
+        <v>0.2138</v>
+      </c>
+      <c r="V98">
+        <v>0.0775975977559997</v>
+      </c>
+      <c r="W98">
+        <v>0.1972096335997673</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.5111380960713189</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.232127497821274</v>
+      </c>
+      <c r="C99">
+        <v>-32.16510519604539</v>
+      </c>
+      <c r="D99">
+        <v>19.55689480395461</v>
+      </c>
+      <c r="E99">
+        <v>32.532</v>
+      </c>
+      <c r="F99">
+        <v>53.932</v>
+      </c>
+      <c r="G99">
+        <v>2.21</v>
+      </c>
+      <c r="H99">
+        <v>34.2</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>6.04</v>
+      </c>
+      <c r="K99">
+        <v>0.207</v>
+      </c>
+      <c r="L99">
+        <v>5.833</v>
+      </c>
+      <c r="M99">
+        <v>11.5306616</v>
+      </c>
+      <c r="N99">
+        <v>-5.6976616</v>
+      </c>
+      <c r="O99">
+        <v>-0.8649812181577562</v>
+      </c>
+      <c r="P99">
+        <v>-4.832680381842244</v>
+      </c>
+      <c r="Q99">
+        <v>-4.625680381842244</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.355608318849915</v>
+      </c>
+      <c r="T99">
+        <v>15.63814757317272</v>
+      </c>
+      <c r="U99">
+        <v>0.2138</v>
+      </c>
+      <c r="V99">
+        <v>0.07679762252140175</v>
+      </c>
+      <c r="W99">
+        <v>0.1973806683049243</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.5058686311633671</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.233877497821274</v>
+      </c>
+      <c r="C100">
+        <v>-32.86770661304269</v>
+      </c>
+      <c r="D100">
+        <v>19.41029338695732</v>
+      </c>
+      <c r="E100">
+        <v>33.088</v>
+      </c>
+      <c r="F100">
+        <v>54.488</v>
+      </c>
+      <c r="G100">
+        <v>2.21</v>
+      </c>
+      <c r="H100">
+        <v>34.2</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>6.04</v>
+      </c>
+      <c r="K100">
+        <v>0.207</v>
+      </c>
+      <c r="L100">
+        <v>5.833</v>
+      </c>
+      <c r="M100">
+        <v>11.6495344</v>
+      </c>
+      <c r="N100">
+        <v>-5.816534399999998</v>
+      </c>
+      <c r="O100">
+        <v>-0.8830276987261743</v>
+      </c>
+      <c r="P100">
+        <v>-4.933506701273824</v>
+      </c>
+      <c r="Q100">
+        <v>-4.726506701273824</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.014012478274872</v>
+      </c>
+      <c r="T100">
+        <v>23.45722135975907</v>
+      </c>
+      <c r="U100">
+        <v>0.2138</v>
+      </c>
+      <c r="V100">
+        <v>0.0760139733119997</v>
+      </c>
+      <c r="W100">
+        <v>0.1975482125058945</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.5007067063555777</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2607103792983925</v>
+      </c>
+      <c r="C101">
+        <v>-35.42471317375907</v>
+      </c>
+      <c r="D101">
+        <v>17.40928682624094</v>
+      </c>
+      <c r="E101">
+        <v>33.64400000000001</v>
+      </c>
+      <c r="F101">
+        <v>55.044</v>
+      </c>
+      <c r="G101">
+        <v>2.21</v>
+      </c>
+      <c r="H101">
+        <v>34.2</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>6.04</v>
+      </c>
+      <c r="K101">
+        <v>0.207</v>
+      </c>
+      <c r="L101">
+        <v>5.833</v>
+      </c>
+      <c r="M101">
+        <v>13.1445072</v>
+      </c>
+      <c r="N101">
+        <v>-7.311507200000001</v>
+      </c>
+      <c r="O101">
+        <v>-1.109984560056218</v>
+      </c>
+      <c r="P101">
+        <v>-6.201522639943783</v>
+      </c>
+      <c r="Q101">
+        <v>-5.994522639943783</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>4.02251310426158</v>
+      </c>
+      <c r="T101">
+        <v>47.30976598631671</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.06736862656812438</v>
+      </c>
+      <c r="W101">
+        <v>0.2227123719755319</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.4437595043502277</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
